--- a/pages/Sprint_Points_Men.xlsx
+++ b/pages/Sprint_Points_Men.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D1FDAC-4EF9-4E86-AE04-15ADAFB8A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint_Points_Men" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -2320,8 +2326,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2384,6 +2390,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2430,7 +2444,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2462,9 +2476,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2496,6 +2528,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2671,11 +2721,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J943"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2707,7 +2757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2739,7 +2789,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2771,7 +2821,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2803,7 +2853,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2835,7 +2885,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2867,7 +2917,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2899,7 +2949,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2931,7 +2981,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2963,7 +3013,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2995,7 +3045,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3027,7 +3077,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3059,7 +3109,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3091,7 +3141,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3123,7 +3173,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -3155,7 +3205,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -3187,7 +3237,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -3219,7 +3269,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -3251,7 +3301,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -3283,7 +3333,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -3315,7 +3365,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -3347,7 +3397,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -3379,7 +3429,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3411,7 +3461,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3443,7 +3493,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3475,7 +3525,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3507,7 +3557,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3539,7 +3589,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3571,7 +3621,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3603,7 +3653,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3635,7 +3685,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3667,7 +3717,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -3699,7 +3749,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -3731,7 +3781,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -3763,7 +3813,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -3795,7 +3845,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -3827,7 +3877,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -3859,7 +3909,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -3891,7 +3941,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -3923,7 +3973,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -3955,7 +4005,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -3987,7 +4037,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -4019,7 +4069,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -4051,7 +4101,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -4083,7 +4133,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -4115,7 +4165,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -4147,7 +4197,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -4179,7 +4229,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -4211,7 +4261,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -4243,7 +4293,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -4275,7 +4325,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -4307,7 +4357,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -4339,7 +4389,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -4371,7 +4421,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -4403,7 +4453,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -4435,7 +4485,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -4467,7 +4517,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -4499,7 +4549,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -4531,7 +4581,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -4563,7 +4613,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -4595,7 +4645,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -4627,7 +4677,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -4659,7 +4709,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -4691,7 +4741,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -4723,7 +4773,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -4755,7 +4805,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -4787,7 +4837,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -4819,7 +4869,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -4851,7 +4901,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -4883,7 +4933,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -4915,7 +4965,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -4947,7 +4997,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -4979,7 +5029,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -5011,7 +5061,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -5043,7 +5093,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -5075,7 +5125,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -5107,7 +5157,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -5139,7 +5189,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -5171,7 +5221,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -5203,7 +5253,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -5235,7 +5285,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -5267,7 +5317,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -5299,7 +5349,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -5331,7 +5381,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -5363,7 +5413,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -5395,7 +5445,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -5427,7 +5477,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -5459,7 +5509,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -5491,7 +5541,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -5523,7 +5573,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -5555,7 +5605,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -5587,7 +5637,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -5619,7 +5669,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -5651,7 +5701,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -5683,7 +5733,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -5715,7 +5765,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -5747,7 +5797,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -5779,7 +5829,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -5811,7 +5861,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -5843,7 +5893,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -5875,7 +5925,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -5907,7 +5957,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -5939,7 +5989,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -5971,7 +6021,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -6003,7 +6053,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -6035,7 +6085,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -6067,7 +6117,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -6099,7 +6149,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -6131,7 +6181,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -6163,7 +6213,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -6195,7 +6245,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -6227,7 +6277,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -6259,7 +6309,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -6291,7 +6341,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -6323,7 +6373,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -6355,7 +6405,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -6387,7 +6437,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -6419,7 +6469,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -6451,7 +6501,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -6483,7 +6533,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -6515,7 +6565,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -6547,7 +6597,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -6579,7 +6629,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -6611,7 +6661,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -6643,7 +6693,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -6675,7 +6725,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -6707,7 +6757,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -6739,7 +6789,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -6771,7 +6821,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -6803,7 +6853,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -6835,7 +6885,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -6867,7 +6917,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -6899,7 +6949,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -6931,7 +6981,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -6963,7 +7013,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -6995,7 +7045,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>20</v>
       </c>
@@ -7027,7 +7077,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -7059,7 +7109,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>20</v>
       </c>
@@ -7091,7 +7141,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>20</v>
       </c>
@@ -7123,7 +7173,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>20</v>
       </c>
@@ -7155,7 +7205,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>20</v>
       </c>
@@ -7187,7 +7237,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7219,7 +7269,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>20</v>
       </c>
@@ -7251,7 +7301,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>20</v>
       </c>
@@ -7283,7 +7333,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>21</v>
       </c>
@@ -7315,7 +7365,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>21</v>
       </c>
@@ -7347,7 +7397,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>21</v>
       </c>
@@ -7379,7 +7429,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>21</v>
       </c>
@@ -7411,7 +7461,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -7443,7 +7493,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>21</v>
       </c>
@@ -7475,7 +7525,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -7507,7 +7557,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -7539,7 +7589,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>21</v>
       </c>
@@ -7571,7 +7621,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -7603,7 +7653,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -7635,7 +7685,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>22</v>
       </c>
@@ -7667,7 +7717,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>22</v>
       </c>
@@ -7699,7 +7749,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>22</v>
       </c>
@@ -7731,7 +7781,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>22</v>
       </c>
@@ -7763,7 +7813,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>22</v>
       </c>
@@ -7795,7 +7845,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>22</v>
       </c>
@@ -7827,7 +7877,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>22</v>
       </c>
@@ -7859,7 +7909,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -7891,7 +7941,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>22</v>
       </c>
@@ -7923,7 +7973,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>22</v>
       </c>
@@ -7955,7 +8005,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>22</v>
       </c>
@@ -7987,7 +8037,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>22</v>
       </c>
@@ -8019,7 +8069,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>22</v>
       </c>
@@ -8051,7 +8101,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -8083,7 +8133,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>23</v>
       </c>
@@ -8115,7 +8165,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -8147,7 +8197,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>23</v>
       </c>
@@ -8179,7 +8229,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>23</v>
       </c>
@@ -8211,7 +8261,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>23</v>
       </c>
@@ -8243,7 +8293,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>23</v>
       </c>
@@ -8275,7 +8325,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>23</v>
       </c>
@@ -8307,7 +8357,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>23</v>
       </c>
@@ -8339,7 +8389,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -8371,7 +8421,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -8403,7 +8453,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>23</v>
       </c>
@@ -8435,7 +8485,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>24</v>
       </c>
@@ -8467,7 +8517,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -8499,7 +8549,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>24</v>
       </c>
@@ -8531,7 +8581,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>24</v>
       </c>
@@ -8563,7 +8613,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>24</v>
       </c>
@@ -8595,7 +8645,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>24</v>
       </c>
@@ -8627,7 +8677,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>24</v>
       </c>
@@ -8659,7 +8709,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>24</v>
       </c>
@@ -8691,7 +8741,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>24</v>
       </c>
@@ -8723,7 +8773,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>24</v>
       </c>
@@ -8755,7 +8805,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>24</v>
       </c>
@@ -8787,7 +8837,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>24</v>
       </c>
@@ -8819,7 +8869,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>24</v>
       </c>
@@ -8851,7 +8901,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -8883,7 +8933,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>24</v>
       </c>
@@ -8915,7 +8965,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>25</v>
       </c>
@@ -8947,7 +8997,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>25</v>
       </c>
@@ -8979,7 +9029,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>25</v>
       </c>
@@ -9011,7 +9061,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>25</v>
       </c>
@@ -9043,7 +9093,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>25</v>
       </c>
@@ -9075,7 +9125,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -9107,7 +9157,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>25</v>
       </c>
@@ -9139,7 +9189,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>25</v>
       </c>
@@ -9171,7 +9221,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -9203,7 +9253,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -9235,7 +9285,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -9267,7 +9317,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -9299,7 +9349,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -9331,7 +9381,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -9363,7 +9413,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -9395,7 +9445,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -9427,7 +9477,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -9459,7 +9509,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -9491,7 +9541,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -9523,7 +9573,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>27</v>
       </c>
@@ -9555,7 +9605,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>27</v>
       </c>
@@ -9587,7 +9637,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -9619,7 +9669,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>27</v>
       </c>
@@ -9651,7 +9701,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>27</v>
       </c>
@@ -9683,7 +9733,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>27</v>
       </c>
@@ -9715,7 +9765,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>27</v>
       </c>
@@ -9747,7 +9797,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>28</v>
       </c>
@@ -9779,7 +9829,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -9811,7 +9861,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>28</v>
       </c>
@@ -9843,7 +9893,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>28</v>
       </c>
@@ -9875,7 +9925,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>28</v>
       </c>
@@ -9907,7 +9957,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>28</v>
       </c>
@@ -9939,7 +9989,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>28</v>
       </c>
@@ -9971,7 +10021,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>28</v>
       </c>
@@ -10003,7 +10053,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>28</v>
       </c>
@@ -10035,7 +10085,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>29</v>
       </c>
@@ -10067,7 +10117,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>29</v>
       </c>
@@ -10099,7 +10149,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>29</v>
       </c>
@@ -10131,7 +10181,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>29</v>
       </c>
@@ -10163,7 +10213,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>29</v>
       </c>
@@ -10195,7 +10245,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>29</v>
       </c>
@@ -10227,7 +10277,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>29</v>
       </c>
@@ -10259,7 +10309,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>29</v>
       </c>
@@ -10291,7 +10341,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>30</v>
       </c>
@@ -10323,7 +10373,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -10355,7 +10405,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>30</v>
       </c>
@@ -10387,7 +10437,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>30</v>
       </c>
@@ -10419,7 +10469,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>30</v>
       </c>
@@ -10451,7 +10501,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>31</v>
       </c>
@@ -10483,7 +10533,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>31</v>
       </c>
@@ -10515,7 +10565,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>31</v>
       </c>
@@ -10547,7 +10597,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>31</v>
       </c>
@@ -10579,7 +10629,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>31</v>
       </c>
@@ -10611,7 +10661,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>31</v>
       </c>
@@ -10643,7 +10693,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>31</v>
       </c>
@@ -10675,7 +10725,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>31</v>
       </c>
@@ -10707,7 +10757,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>31</v>
       </c>
@@ -10739,7 +10789,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>31</v>
       </c>
@@ -10771,7 +10821,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>31</v>
       </c>
@@ -10803,7 +10853,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>31</v>
       </c>
@@ -10835,7 +10885,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>31</v>
       </c>
@@ -10867,7 +10917,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>31</v>
       </c>
@@ -10899,7 +10949,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>31</v>
       </c>
@@ -10931,7 +10981,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>31</v>
       </c>
@@ -10963,7 +11013,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>32</v>
       </c>
@@ -10995,7 +11045,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>32</v>
       </c>
@@ -11027,7 +11077,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>32</v>
       </c>
@@ -11059,7 +11109,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>32</v>
       </c>
@@ -11091,7 +11141,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>32</v>
       </c>
@@ -11123,7 +11173,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>32</v>
       </c>
@@ -11155,7 +11205,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>32</v>
       </c>
@@ -11187,7 +11237,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>32</v>
       </c>
@@ -11219,7 +11269,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>32</v>
       </c>
@@ -11251,7 +11301,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>32</v>
       </c>
@@ -11283,7 +11333,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>32</v>
       </c>
@@ -11315,7 +11365,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>32</v>
       </c>
@@ -11347,7 +11397,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>32</v>
       </c>
@@ -11379,7 +11429,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>33</v>
       </c>
@@ -11411,7 +11461,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>33</v>
       </c>
@@ -11443,7 +11493,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>33</v>
       </c>
@@ -11475,7 +11525,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>33</v>
       </c>
@@ -11507,7 +11557,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>33</v>
       </c>
@@ -11539,7 +11589,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>33</v>
       </c>
@@ -11571,7 +11621,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>33</v>
       </c>
@@ -11603,7 +11653,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>33</v>
       </c>
@@ -11635,7 +11685,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>33</v>
       </c>
@@ -11667,7 +11717,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>33</v>
       </c>
@@ -11699,7 +11749,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>33</v>
       </c>
@@ -11731,7 +11781,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>33</v>
       </c>
@@ -11763,7 +11813,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>33</v>
       </c>
@@ -11795,7 +11845,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>33</v>
       </c>
@@ -11827,7 +11877,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>34</v>
       </c>
@@ -11859,7 +11909,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>34</v>
       </c>
@@ -11891,7 +11941,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>34</v>
       </c>
@@ -11923,7 +11973,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>34</v>
       </c>
@@ -11955,7 +12005,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>34</v>
       </c>
@@ -11987,7 +12037,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>34</v>
       </c>
@@ -12019,7 +12069,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>34</v>
       </c>
@@ -12051,7 +12101,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>35</v>
       </c>
@@ -12083,7 +12133,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>35</v>
       </c>
@@ -12115,7 +12165,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>35</v>
       </c>
@@ -12147,7 +12197,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>35</v>
       </c>
@@ -12179,7 +12229,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>35</v>
       </c>
@@ -12211,7 +12261,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>35</v>
       </c>
@@ -12243,7 +12293,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>35</v>
       </c>
@@ -12275,7 +12325,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>35</v>
       </c>
@@ -12307,7 +12357,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>35</v>
       </c>
@@ -12339,7 +12389,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>35</v>
       </c>
@@ -12371,7 +12421,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>35</v>
       </c>
@@ -12403,7 +12453,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>35</v>
       </c>
@@ -12435,7 +12485,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>35</v>
       </c>
@@ -12467,7 +12517,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>35</v>
       </c>
@@ -12499,7 +12549,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>36</v>
       </c>
@@ -12531,7 +12581,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>36</v>
       </c>
@@ -12563,7 +12613,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>36</v>
       </c>
@@ -12595,7 +12645,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>36</v>
       </c>
@@ -12627,7 +12677,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>36</v>
       </c>
@@ -12659,7 +12709,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>36</v>
       </c>
@@ -12691,7 +12741,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>36</v>
       </c>
@@ -12723,7 +12773,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>37</v>
       </c>
@@ -12755,7 +12805,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>37</v>
       </c>
@@ -12787,7 +12837,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>37</v>
       </c>
@@ -12819,7 +12869,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>37</v>
       </c>
@@ -12851,7 +12901,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>37</v>
       </c>
@@ -12883,7 +12933,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>37</v>
       </c>
@@ -12915,7 +12965,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>37</v>
       </c>
@@ -12947,7 +12997,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>37</v>
       </c>
@@ -12979,7 +13029,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>37</v>
       </c>
@@ -13011,7 +13061,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>37</v>
       </c>
@@ -13043,7 +13093,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>37</v>
       </c>
@@ -13075,7 +13125,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>37</v>
       </c>
@@ -13107,7 +13157,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>37</v>
       </c>
@@ -13139,7 +13189,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>37</v>
       </c>
@@ -13171,7 +13221,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>37</v>
       </c>
@@ -13203,7 +13253,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>37</v>
       </c>
@@ -13235,7 +13285,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>37</v>
       </c>
@@ -13267,7 +13317,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>37</v>
       </c>
@@ -13299,7 +13349,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>38</v>
       </c>
@@ -13331,7 +13381,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>38</v>
       </c>
@@ -13363,7 +13413,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>38</v>
       </c>
@@ -13395,7 +13445,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>38</v>
       </c>
@@ -13427,7 +13477,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>38</v>
       </c>
@@ -13459,7 +13509,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>38</v>
       </c>
@@ -13491,7 +13541,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>38</v>
       </c>
@@ -13523,7 +13573,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>38</v>
       </c>
@@ -13555,7 +13605,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>38</v>
       </c>
@@ -13587,7 +13637,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>39</v>
       </c>
@@ -13619,7 +13669,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>39</v>
       </c>
@@ -13651,7 +13701,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>39</v>
       </c>
@@ -13683,7 +13733,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>39</v>
       </c>
@@ -13715,7 +13765,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>39</v>
       </c>
@@ -13747,7 +13797,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>39</v>
       </c>
@@ -13779,7 +13829,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>39</v>
       </c>
@@ -13811,7 +13861,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>39</v>
       </c>
@@ -13843,7 +13893,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>40</v>
       </c>
@@ -13875,7 +13925,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>40</v>
       </c>
@@ -13907,7 +13957,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>40</v>
       </c>
@@ -13939,7 +13989,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>40</v>
       </c>
@@ -13971,7 +14021,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>40</v>
       </c>
@@ -14003,7 +14053,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>40</v>
       </c>
@@ -14035,7 +14085,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>40</v>
       </c>
@@ -14067,7 +14117,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>40</v>
       </c>
@@ -14099,7 +14149,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>41</v>
       </c>
@@ -14131,7 +14181,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>41</v>
       </c>
@@ -14163,7 +14213,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>41</v>
       </c>
@@ -14195,7 +14245,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>41</v>
       </c>
@@ -14227,7 +14277,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>41</v>
       </c>
@@ -14259,7 +14309,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>41</v>
       </c>
@@ -14291,7 +14341,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>41</v>
       </c>
@@ -14323,7 +14373,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>41</v>
       </c>
@@ -14355,7 +14405,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>41</v>
       </c>
@@ -14387,7 +14437,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>41</v>
       </c>
@@ -14419,7 +14469,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>41</v>
       </c>
@@ -14451,7 +14501,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>42</v>
       </c>
@@ -14483,7 +14533,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>42</v>
       </c>
@@ -14515,7 +14565,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>42</v>
       </c>
@@ -14547,7 +14597,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>42</v>
       </c>
@@ -14579,7 +14629,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>42</v>
       </c>
@@ -14611,7 +14661,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>42</v>
       </c>
@@ -14643,7 +14693,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>42</v>
       </c>
@@ -14675,7 +14725,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>42</v>
       </c>
@@ -14707,7 +14757,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>43</v>
       </c>
@@ -14739,7 +14789,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>43</v>
       </c>
@@ -14771,7 +14821,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>43</v>
       </c>
@@ -14803,7 +14853,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>43</v>
       </c>
@@ -14835,7 +14885,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>43</v>
       </c>
@@ -14867,7 +14917,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>43</v>
       </c>
@@ -14899,7 +14949,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>43</v>
       </c>
@@ -14931,7 +14981,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>43</v>
       </c>
@@ -14963,7 +15013,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>43</v>
       </c>
@@ -14995,7 +15045,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>43</v>
       </c>
@@ -15027,7 +15077,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>43</v>
       </c>
@@ -15059,7 +15109,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>43</v>
       </c>
@@ -15091,7 +15141,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>44</v>
       </c>
@@ -15123,7 +15173,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>44</v>
       </c>
@@ -15155,7 +15205,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>44</v>
       </c>
@@ -15187,7 +15237,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>44</v>
       </c>
@@ -15219,7 +15269,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>44</v>
       </c>
@@ -15251,7 +15301,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>44</v>
       </c>
@@ -15283,7 +15333,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>44</v>
       </c>
@@ -15315,7 +15365,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>45</v>
       </c>
@@ -15347,7 +15397,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>45</v>
       </c>
@@ -15379,7 +15429,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>45</v>
       </c>
@@ -15411,7 +15461,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>45</v>
       </c>
@@ -15443,7 +15493,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>45</v>
       </c>
@@ -15475,7 +15525,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>45</v>
       </c>
@@ -15507,7 +15557,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>45</v>
       </c>
@@ -15539,7 +15589,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>45</v>
       </c>
@@ -15571,7 +15621,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>45</v>
       </c>
@@ -15603,7 +15653,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>45</v>
       </c>
@@ -15635,7 +15685,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>45</v>
       </c>
@@ -15667,7 +15717,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>45</v>
       </c>
@@ -15699,7 +15749,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>45</v>
       </c>
@@ -15731,7 +15781,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>45</v>
       </c>
@@ -15763,7 +15813,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>45</v>
       </c>
@@ -15795,7 +15845,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>46</v>
       </c>
@@ -15827,7 +15877,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>46</v>
       </c>
@@ -15859,7 +15909,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>46</v>
       </c>
@@ -15891,7 +15941,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="414" spans="1:10">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>46</v>
       </c>
@@ -15923,7 +15973,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>46</v>
       </c>
@@ -15955,7 +16005,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>46</v>
       </c>
@@ -15987,7 +16037,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>46</v>
       </c>
@@ -16019,7 +16069,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>46</v>
       </c>
@@ -16051,7 +16101,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>47</v>
       </c>
@@ -16083,7 +16133,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>47</v>
       </c>
@@ -16115,7 +16165,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>47</v>
       </c>
@@ -16147,7 +16197,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>47</v>
       </c>
@@ -16179,7 +16229,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>47</v>
       </c>
@@ -16211,7 +16261,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>47</v>
       </c>
@@ -16243,7 +16293,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>47</v>
       </c>
@@ -16275,7 +16325,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>47</v>
       </c>
@@ -16307,7 +16357,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>47</v>
       </c>
@@ -16339,7 +16389,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="428" spans="1:10">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>47</v>
       </c>
@@ -16371,7 +16421,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="429" spans="1:10">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>47</v>
       </c>
@@ -16403,7 +16453,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="430" spans="1:10">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>48</v>
       </c>
@@ -16435,7 +16485,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="431" spans="1:10">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>48</v>
       </c>
@@ -16467,7 +16517,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>48</v>
       </c>
@@ -16499,7 +16549,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="433" spans="1:10">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>48</v>
       </c>
@@ -16531,7 +16581,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>48</v>
       </c>
@@ -16563,7 +16613,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="435" spans="1:10">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>48</v>
       </c>
@@ -16595,7 +16645,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>48</v>
       </c>
@@ -16627,7 +16677,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>48</v>
       </c>
@@ -16659,7 +16709,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>48</v>
       </c>
@@ -16691,7 +16741,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="439" spans="1:10">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>48</v>
       </c>
@@ -16723,7 +16773,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="440" spans="1:10">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>48</v>
       </c>
@@ -16755,7 +16805,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>49</v>
       </c>
@@ -16787,7 +16837,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>49</v>
       </c>
@@ -16819,7 +16869,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>49</v>
       </c>
@@ -16851,7 +16901,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>49</v>
       </c>
@@ -16883,7 +16933,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>49</v>
       </c>
@@ -16915,7 +16965,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="446" spans="1:10">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>49</v>
       </c>
@@ -16947,7 +16997,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>49</v>
       </c>
@@ -16979,7 +17029,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>49</v>
       </c>
@@ -17011,7 +17061,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="449" spans="1:10">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>49</v>
       </c>
@@ -17043,7 +17093,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>49</v>
       </c>
@@ -17075,7 +17125,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>49</v>
       </c>
@@ -17107,7 +17157,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>49</v>
       </c>
@@ -17139,7 +17189,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>49</v>
       </c>
@@ -17171,7 +17221,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>49</v>
       </c>
@@ -17203,7 +17253,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>49</v>
       </c>
@@ -17235,7 +17285,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>50</v>
       </c>
@@ -17267,7 +17317,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>50</v>
       </c>
@@ -17299,7 +17349,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>50</v>
       </c>
@@ -17331,7 +17381,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>50</v>
       </c>
@@ -17363,7 +17413,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>50</v>
       </c>
@@ -17395,7 +17445,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>50</v>
       </c>
@@ -17427,7 +17477,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>50</v>
       </c>
@@ -17459,7 +17509,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>50</v>
       </c>
@@ -17491,7 +17541,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>50</v>
       </c>
@@ -17523,7 +17573,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>50</v>
       </c>
@@ -17555,7 +17605,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>50</v>
       </c>
@@ -17587,7 +17637,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>50</v>
       </c>
@@ -17619,7 +17669,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>51</v>
       </c>
@@ -17651,7 +17701,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>51</v>
       </c>
@@ -17683,7 +17733,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>51</v>
       </c>
@@ -17715,7 +17765,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>51</v>
       </c>
@@ -17747,7 +17797,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>51</v>
       </c>
@@ -17779,7 +17829,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>51</v>
       </c>
@@ -17811,7 +17861,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>51</v>
       </c>
@@ -17843,7 +17893,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>51</v>
       </c>
@@ -17875,7 +17925,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>51</v>
       </c>
@@ -17907,7 +17957,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>51</v>
       </c>
@@ -17939,7 +17989,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>52</v>
       </c>
@@ -17971,7 +18021,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>52</v>
       </c>
@@ -18003,7 +18053,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>52</v>
       </c>
@@ -18035,7 +18085,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>52</v>
       </c>
@@ -18067,7 +18117,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>52</v>
       </c>
@@ -18099,7 +18149,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>52</v>
       </c>
@@ -18131,7 +18181,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>52</v>
       </c>
@@ -18163,7 +18213,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>52</v>
       </c>
@@ -18195,7 +18245,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>52</v>
       </c>
@@ -18227,7 +18277,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>53</v>
       </c>
@@ -18259,7 +18309,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="488" spans="1:10">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>53</v>
       </c>
@@ -18291,7 +18341,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="489" spans="1:10">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>53</v>
       </c>
@@ -18323,7 +18373,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="490" spans="1:10">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>53</v>
       </c>
@@ -18355,7 +18405,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="491" spans="1:10">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>53</v>
       </c>
@@ -18387,7 +18437,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>53</v>
       </c>
@@ -18419,7 +18469,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="493" spans="1:10">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>53</v>
       </c>
@@ -18451,7 +18501,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="494" spans="1:10">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>53</v>
       </c>
@@ -18483,7 +18533,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="495" spans="1:10">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>53</v>
       </c>
@@ -18515,7 +18565,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="496" spans="1:10">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>54</v>
       </c>
@@ -18547,7 +18597,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>54</v>
       </c>
@@ -18579,7 +18629,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="498" spans="1:10">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>54</v>
       </c>
@@ -18611,7 +18661,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>54</v>
       </c>
@@ -18643,7 +18693,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="500" spans="1:10">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>54</v>
       </c>
@@ -18675,7 +18725,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="501" spans="1:10">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>54</v>
       </c>
@@ -18707,7 +18757,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="502" spans="1:10">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>54</v>
       </c>
@@ -18739,7 +18789,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="503" spans="1:10">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
         <v>54</v>
       </c>
@@ -18771,7 +18821,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="504" spans="1:10">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>55</v>
       </c>
@@ -18803,7 +18853,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="505" spans="1:10">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>55</v>
       </c>
@@ -18835,7 +18885,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="506" spans="1:10">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>55</v>
       </c>
@@ -18867,7 +18917,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="507" spans="1:10">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>55</v>
       </c>
@@ -18899,7 +18949,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="508" spans="1:10">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>55</v>
       </c>
@@ -18931,7 +18981,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="509" spans="1:10">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>55</v>
       </c>
@@ -18963,7 +19013,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="510" spans="1:10">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>55</v>
       </c>
@@ -18995,7 +19045,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="511" spans="1:10">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>56</v>
       </c>
@@ -19027,7 +19077,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="512" spans="1:10">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>56</v>
       </c>
@@ -19059,7 +19109,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="513" spans="1:10">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>56</v>
       </c>
@@ -19091,7 +19141,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="514" spans="1:10">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>56</v>
       </c>
@@ -19123,7 +19173,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="515" spans="1:10">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>56</v>
       </c>
@@ -19155,7 +19205,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="516" spans="1:10">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>56</v>
       </c>
@@ -19187,7 +19237,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="517" spans="1:10">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>56</v>
       </c>
@@ -19219,7 +19269,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="518" spans="1:10">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>57</v>
       </c>
@@ -19251,7 +19301,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="519" spans="1:10">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>57</v>
       </c>
@@ -19283,7 +19333,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="520" spans="1:10">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>57</v>
       </c>
@@ -19315,7 +19365,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="521" spans="1:10">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>57</v>
       </c>
@@ -19347,7 +19397,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="522" spans="1:10">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>57</v>
       </c>
@@ -19379,7 +19429,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="523" spans="1:10">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>57</v>
       </c>
@@ -19411,7 +19461,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="524" spans="1:10">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>57</v>
       </c>
@@ -19443,7 +19493,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="525" spans="1:10">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>57</v>
       </c>
@@ -19475,7 +19525,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="526" spans="1:10">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>57</v>
       </c>
@@ -19507,7 +19557,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="527" spans="1:10">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>57</v>
       </c>
@@ -19539,7 +19589,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="528" spans="1:10">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>57</v>
       </c>
@@ -19571,7 +19621,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="529" spans="1:10">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>57</v>
       </c>
@@ -19603,7 +19653,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="530" spans="1:10">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>57</v>
       </c>
@@ -19635,7 +19685,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="531" spans="1:10">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>57</v>
       </c>
@@ -19667,7 +19717,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="532" spans="1:10">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>57</v>
       </c>
@@ -19699,7 +19749,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="533" spans="1:10">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>58</v>
       </c>
@@ -19731,7 +19781,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="534" spans="1:10">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>58</v>
       </c>
@@ -19763,7 +19813,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="535" spans="1:10">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>58</v>
       </c>
@@ -19795,7 +19845,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="536" spans="1:10">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>58</v>
       </c>
@@ -19827,7 +19877,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="537" spans="1:10">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>58</v>
       </c>
@@ -19859,7 +19909,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="538" spans="1:10">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>58</v>
       </c>
@@ -19891,7 +19941,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="539" spans="1:10">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>58</v>
       </c>
@@ -19923,7 +19973,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="540" spans="1:10">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>58</v>
       </c>
@@ -19955,7 +20005,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="541" spans="1:10">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>58</v>
       </c>
@@ -19987,7 +20037,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="542" spans="1:10">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>59</v>
       </c>
@@ -20019,7 +20069,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="543" spans="1:10">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>59</v>
       </c>
@@ -20051,7 +20101,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="544" spans="1:10">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>59</v>
       </c>
@@ -20083,7 +20133,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="545" spans="1:10">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>59</v>
       </c>
@@ -20115,7 +20165,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="546" spans="1:10">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>60</v>
       </c>
@@ -20147,7 +20197,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>60</v>
       </c>
@@ -20179,7 +20229,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="548" spans="1:10">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>60</v>
       </c>
@@ -20211,7 +20261,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="549" spans="1:10">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>60</v>
       </c>
@@ -20243,7 +20293,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="550" spans="1:10">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>60</v>
       </c>
@@ -20275,7 +20325,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="551" spans="1:10">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>60</v>
       </c>
@@ -20307,7 +20357,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>60</v>
       </c>
@@ -20339,7 +20389,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="553" spans="1:10">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>61</v>
       </c>
@@ -20371,7 +20421,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="554" spans="1:10">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>61</v>
       </c>
@@ -20403,7 +20453,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="555" spans="1:10">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>61</v>
       </c>
@@ -20435,7 +20485,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="556" spans="1:10">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>61</v>
       </c>
@@ -20467,7 +20517,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>61</v>
       </c>
@@ -20499,7 +20549,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="558" spans="1:10">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>61</v>
       </c>
@@ -20531,7 +20581,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="559" spans="1:10">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>61</v>
       </c>
@@ -20563,7 +20613,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="560" spans="1:10">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>62</v>
       </c>
@@ -20595,7 +20645,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="561" spans="1:10">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>62</v>
       </c>
@@ -20627,7 +20677,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="562" spans="1:10">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>62</v>
       </c>
@@ -20659,7 +20709,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="563" spans="1:10">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>62</v>
       </c>
@@ -20691,7 +20741,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="564" spans="1:10">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>63</v>
       </c>
@@ -20723,7 +20773,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="565" spans="1:10">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>63</v>
       </c>
@@ -20755,7 +20805,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="566" spans="1:10">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>63</v>
       </c>
@@ -20787,7 +20837,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="567" spans="1:10">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>63</v>
       </c>
@@ -20819,7 +20869,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="568" spans="1:10">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>64</v>
       </c>
@@ -20851,7 +20901,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="569" spans="1:10">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>64</v>
       </c>
@@ -20883,7 +20933,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="570" spans="1:10">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>64</v>
       </c>
@@ -20915,7 +20965,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="571" spans="1:10">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>64</v>
       </c>
@@ -20947,7 +20997,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="572" spans="1:10">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>64</v>
       </c>
@@ -20979,7 +21029,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="573" spans="1:10">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>64</v>
       </c>
@@ -21011,7 +21061,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="574" spans="1:10">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>64</v>
       </c>
@@ -21043,7 +21093,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="575" spans="1:10">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>64</v>
       </c>
@@ -21075,7 +21125,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="576" spans="1:10">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>65</v>
       </c>
@@ -21107,7 +21157,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="577" spans="1:10">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>65</v>
       </c>
@@ -21139,7 +21189,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="578" spans="1:10">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>65</v>
       </c>
@@ -21171,7 +21221,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="579" spans="1:10">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>65</v>
       </c>
@@ -21203,7 +21253,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="580" spans="1:10">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>65</v>
       </c>
@@ -21235,7 +21285,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="581" spans="1:10">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>65</v>
       </c>
@@ -21267,7 +21317,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="582" spans="1:10">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>65</v>
       </c>
@@ -21299,7 +21349,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="583" spans="1:10">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>65</v>
       </c>
@@ -21331,7 +21381,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="584" spans="1:10">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>66</v>
       </c>
@@ -21363,7 +21413,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="585" spans="1:10">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>66</v>
       </c>
@@ -21395,7 +21445,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="586" spans="1:10">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>66</v>
       </c>
@@ -21427,7 +21477,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="587" spans="1:10">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>66</v>
       </c>
@@ -21459,7 +21509,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="588" spans="1:10">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>66</v>
       </c>
@@ -21491,7 +21541,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="589" spans="1:10">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>67</v>
       </c>
@@ -21523,7 +21573,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="590" spans="1:10">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>67</v>
       </c>
@@ -21555,7 +21605,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="591" spans="1:10">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>67</v>
       </c>
@@ -21587,7 +21637,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="592" spans="1:10">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>67</v>
       </c>
@@ -21619,7 +21669,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="593" spans="1:10">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>67</v>
       </c>
@@ -21651,7 +21701,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="594" spans="1:10">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>67</v>
       </c>
@@ -21683,7 +21733,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="595" spans="1:10">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>67</v>
       </c>
@@ -21715,7 +21765,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>68</v>
       </c>
@@ -21747,7 +21797,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>68</v>
       </c>
@@ -21779,7 +21829,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>68</v>
       </c>
@@ -21811,7 +21861,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="599" spans="1:10">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>68</v>
       </c>
@@ -21843,7 +21893,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>68</v>
       </c>
@@ -21875,7 +21925,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="601" spans="1:10">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>68</v>
       </c>
@@ -21907,7 +21957,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="602" spans="1:10">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>68</v>
       </c>
@@ -21939,7 +21989,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="603" spans="1:10">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>68</v>
       </c>
@@ -21971,7 +22021,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="604" spans="1:10">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>68</v>
       </c>
@@ -22003,7 +22053,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="605" spans="1:10">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>69</v>
       </c>
@@ -22035,7 +22085,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="606" spans="1:10">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>69</v>
       </c>
@@ -22067,7 +22117,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="607" spans="1:10">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>69</v>
       </c>
@@ -22099,7 +22149,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="608" spans="1:10">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>69</v>
       </c>
@@ -22131,7 +22181,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="609" spans="1:10">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>69</v>
       </c>
@@ -22163,7 +22213,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="610" spans="1:10">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>69</v>
       </c>
@@ -22195,7 +22245,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="611" spans="1:10">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>69</v>
       </c>
@@ -22227,7 +22277,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="612" spans="1:10">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>69</v>
       </c>
@@ -22259,7 +22309,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="613" spans="1:10">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>69</v>
       </c>
@@ -22291,7 +22341,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="614" spans="1:10">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>69</v>
       </c>
@@ -22323,7 +22373,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="615" spans="1:10">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>70</v>
       </c>
@@ -22355,7 +22405,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="616" spans="1:10">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>70</v>
       </c>
@@ -22387,7 +22437,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="617" spans="1:10">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>70</v>
       </c>
@@ -22419,7 +22469,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="618" spans="1:10">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>70</v>
       </c>
@@ -22451,7 +22501,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="619" spans="1:10">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>70</v>
       </c>
@@ -22483,7 +22533,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="620" spans="1:10">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>70</v>
       </c>
@@ -22515,7 +22565,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="621" spans="1:10">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>70</v>
       </c>
@@ -22547,7 +22597,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="622" spans="1:10">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>70</v>
       </c>
@@ -22579,7 +22629,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="623" spans="1:10">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>70</v>
       </c>
@@ -22611,7 +22661,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="624" spans="1:10">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>71</v>
       </c>
@@ -22643,7 +22693,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="625" spans="1:10">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>71</v>
       </c>
@@ -22675,7 +22725,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="626" spans="1:10">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>71</v>
       </c>
@@ -22707,7 +22757,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="627" spans="1:10">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>72</v>
       </c>
@@ -22739,7 +22789,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="628" spans="1:10">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>72</v>
       </c>
@@ -22771,7 +22821,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="629" spans="1:10">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>72</v>
       </c>
@@ -22803,7 +22853,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="630" spans="1:10">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>72</v>
       </c>
@@ -22835,7 +22885,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="631" spans="1:10">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>72</v>
       </c>
@@ -22867,7 +22917,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="632" spans="1:10">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>73</v>
       </c>
@@ -22899,7 +22949,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="633" spans="1:10">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>73</v>
       </c>
@@ -22931,7 +22981,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="634" spans="1:10">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>73</v>
       </c>
@@ -22963,7 +23013,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="635" spans="1:10">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>73</v>
       </c>
@@ -22995,7 +23045,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="636" spans="1:10">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>73</v>
       </c>
@@ -23027,7 +23077,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="637" spans="1:10">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>73</v>
       </c>
@@ -23059,7 +23109,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="638" spans="1:10">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>73</v>
       </c>
@@ -23091,7 +23141,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="639" spans="1:10">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>73</v>
       </c>
@@ -23123,7 +23173,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="640" spans="1:10">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>74</v>
       </c>
@@ -23155,7 +23205,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="641" spans="1:10">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>74</v>
       </c>
@@ -23187,7 +23237,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="642" spans="1:10">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>74</v>
       </c>
@@ -23219,7 +23269,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="643" spans="1:10">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>74</v>
       </c>
@@ -23251,7 +23301,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="644" spans="1:10">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>74</v>
       </c>
@@ -23283,7 +23333,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="645" spans="1:10">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>74</v>
       </c>
@@ -23315,7 +23365,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="646" spans="1:10">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>74</v>
       </c>
@@ -23347,7 +23397,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="647" spans="1:10">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>74</v>
       </c>
@@ -23379,7 +23429,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="648" spans="1:10">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>75</v>
       </c>
@@ -23411,7 +23461,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="649" spans="1:10">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>75</v>
       </c>
@@ -23443,7 +23493,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="650" spans="1:10">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>75</v>
       </c>
@@ -23475,7 +23525,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="651" spans="1:10">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>75</v>
       </c>
@@ -23507,7 +23557,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="652" spans="1:10">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>75</v>
       </c>
@@ -23539,7 +23589,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="653" spans="1:10">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>76</v>
       </c>
@@ -23571,7 +23621,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="654" spans="1:10">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>76</v>
       </c>
@@ -23603,7 +23653,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="655" spans="1:10">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>76</v>
       </c>
@@ -23635,7 +23685,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="656" spans="1:10">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>76</v>
       </c>
@@ -23667,7 +23717,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="657" spans="1:10">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>77</v>
       </c>
@@ -23699,7 +23749,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="658" spans="1:10">
+    <row r="658" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>77</v>
       </c>
@@ -23731,7 +23781,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="659" spans="1:10">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>77</v>
       </c>
@@ -23763,7 +23813,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="660" spans="1:10">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>77</v>
       </c>
@@ -23795,7 +23845,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="661" spans="1:10">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>77</v>
       </c>
@@ -23827,7 +23877,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="662" spans="1:10">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>78</v>
       </c>
@@ -23859,7 +23909,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="663" spans="1:10">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>78</v>
       </c>
@@ -23891,7 +23941,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="664" spans="1:10">
+    <row r="664" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>78</v>
       </c>
@@ -23923,7 +23973,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="665" spans="1:10">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>78</v>
       </c>
@@ -23955,7 +24005,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="666" spans="1:10">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>79</v>
       </c>
@@ -23987,7 +24037,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="667" spans="1:10">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>79</v>
       </c>
@@ -24019,7 +24069,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="668" spans="1:10">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>79</v>
       </c>
@@ -24051,7 +24101,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="669" spans="1:10">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>79</v>
       </c>
@@ -24083,7 +24133,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="670" spans="1:10">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>79</v>
       </c>
@@ -24115,7 +24165,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="671" spans="1:10">
+    <row r="671" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>79</v>
       </c>
@@ -24147,7 +24197,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="672" spans="1:10">
+    <row r="672" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>79</v>
       </c>
@@ -24179,7 +24229,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="673" spans="1:10">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>79</v>
       </c>
@@ -24211,7 +24261,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="674" spans="1:10">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>79</v>
       </c>
@@ -24243,7 +24293,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="675" spans="1:10">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>79</v>
       </c>
@@ -24275,7 +24325,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="676" spans="1:10">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>79</v>
       </c>
@@ -24307,7 +24357,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="677" spans="1:10">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>79</v>
       </c>
@@ -24339,7 +24389,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="678" spans="1:10">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>80</v>
       </c>
@@ -24371,7 +24421,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="679" spans="1:10">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>80</v>
       </c>
@@ -24403,7 +24453,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="680" spans="1:10">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>80</v>
       </c>
@@ -24435,7 +24485,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="681" spans="1:10">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>81</v>
       </c>
@@ -24467,7 +24517,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="682" spans="1:10">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>81</v>
       </c>
@@ -24499,7 +24549,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="683" spans="1:10">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>81</v>
       </c>
@@ -24531,7 +24581,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="684" spans="1:10">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>82</v>
       </c>
@@ -24563,7 +24613,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="685" spans="1:10">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>82</v>
       </c>
@@ -24595,7 +24645,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="686" spans="1:10">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>82</v>
       </c>
@@ -24627,7 +24677,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="687" spans="1:10">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>82</v>
       </c>
@@ -24659,7 +24709,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="688" spans="1:10">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>82</v>
       </c>
@@ -24691,7 +24741,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="689" spans="1:10">
+    <row r="689" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>82</v>
       </c>
@@ -24723,7 +24773,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="690" spans="1:10">
+    <row r="690" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>83</v>
       </c>
@@ -24755,7 +24805,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="691" spans="1:10">
+    <row r="691" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>83</v>
       </c>
@@ -24787,7 +24837,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="692" spans="1:10">
+    <row r="692" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>83</v>
       </c>
@@ -24819,7 +24869,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="693" spans="1:10">
+    <row r="693" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>83</v>
       </c>
@@ -24851,7 +24901,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="694" spans="1:10">
+    <row r="694" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>83</v>
       </c>
@@ -24883,7 +24933,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="695" spans="1:10">
+    <row r="695" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>84</v>
       </c>
@@ -24915,7 +24965,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="696" spans="1:10">
+    <row r="696" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>84</v>
       </c>
@@ -24947,7 +24997,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="697" spans="1:10">
+    <row r="697" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>84</v>
       </c>
@@ -24979,7 +25029,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="698" spans="1:10">
+    <row r="698" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>85</v>
       </c>
@@ -25011,7 +25061,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="699" spans="1:10">
+    <row r="699" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>85</v>
       </c>
@@ -25043,7 +25093,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="700" spans="1:10">
+    <row r="700" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>86</v>
       </c>
@@ -25075,7 +25125,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="701" spans="1:10">
+    <row r="701" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>86</v>
       </c>
@@ -25107,7 +25157,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="702" spans="1:10">
+    <row r="702" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>86</v>
       </c>
@@ -25139,7 +25189,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="703" spans="1:10">
+    <row r="703" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>86</v>
       </c>
@@ -25171,7 +25221,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="704" spans="1:10">
+    <row r="704" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>86</v>
       </c>
@@ -25203,7 +25253,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="705" spans="1:10">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>86</v>
       </c>
@@ -25235,7 +25285,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="706" spans="1:10">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>87</v>
       </c>
@@ -25267,7 +25317,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="707" spans="1:10">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>87</v>
       </c>
@@ -25299,7 +25349,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="708" spans="1:10">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>87</v>
       </c>
@@ -25331,7 +25381,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="709" spans="1:10">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>87</v>
       </c>
@@ -25363,7 +25413,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="710" spans="1:10">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>87</v>
       </c>
@@ -25395,7 +25445,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="711" spans="1:10">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>87</v>
       </c>
@@ -25427,7 +25477,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="712" spans="1:10">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>88</v>
       </c>
@@ -25459,7 +25509,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="713" spans="1:10">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>88</v>
       </c>
@@ -25491,7 +25541,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="714" spans="1:10">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>88</v>
       </c>
@@ -25523,7 +25573,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="715" spans="1:10">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>88</v>
       </c>
@@ -25555,7 +25605,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="716" spans="1:10">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>89</v>
       </c>
@@ -25587,7 +25637,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="717" spans="1:10">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>89</v>
       </c>
@@ -25619,7 +25669,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="718" spans="1:10">
+    <row r="718" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>89</v>
       </c>
@@ -25651,7 +25701,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="719" spans="1:10">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>89</v>
       </c>
@@ -25683,7 +25733,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="720" spans="1:10">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>89</v>
       </c>
@@ -25715,7 +25765,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="721" spans="1:10">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>89</v>
       </c>
@@ -25747,7 +25797,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="722" spans="1:10">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>89</v>
       </c>
@@ -25779,7 +25829,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="723" spans="1:10">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>89</v>
       </c>
@@ -25811,7 +25861,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="724" spans="1:10">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>89</v>
       </c>
@@ -25843,7 +25893,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="725" spans="1:10">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>89</v>
       </c>
@@ -25875,7 +25925,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="726" spans="1:10">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>90</v>
       </c>
@@ -25907,7 +25957,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="727" spans="1:10">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>90</v>
       </c>
@@ -25939,7 +25989,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="728" spans="1:10">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>91</v>
       </c>
@@ -25971,7 +26021,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="729" spans="1:10">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>91</v>
       </c>
@@ -26003,7 +26053,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="730" spans="1:10">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>91</v>
       </c>
@@ -26035,7 +26085,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="731" spans="1:10">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>91</v>
       </c>
@@ -26067,7 +26117,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="732" spans="1:10">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>91</v>
       </c>
@@ -26099,7 +26149,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="733" spans="1:10">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>91</v>
       </c>
@@ -26131,7 +26181,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="734" spans="1:10">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>91</v>
       </c>
@@ -26163,7 +26213,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="735" spans="1:10">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>91</v>
       </c>
@@ -26195,7 +26245,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="736" spans="1:10">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>91</v>
       </c>
@@ -26227,7 +26277,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="737" spans="1:10">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>92</v>
       </c>
@@ -26259,7 +26309,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="738" spans="1:10">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>92</v>
       </c>
@@ -26291,7 +26341,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="739" spans="1:10">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>92</v>
       </c>
@@ -26323,7 +26373,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="740" spans="1:10">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>92</v>
       </c>
@@ -26355,7 +26405,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="741" spans="1:10">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>92</v>
       </c>
@@ -26387,7 +26437,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="742" spans="1:10">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>93</v>
       </c>
@@ -26419,7 +26469,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="743" spans="1:10">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>93</v>
       </c>
@@ -26451,7 +26501,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="744" spans="1:10">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>94</v>
       </c>
@@ -26483,7 +26533,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="745" spans="1:10">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>94</v>
       </c>
@@ -26515,7 +26565,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="746" spans="1:10">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>94</v>
       </c>
@@ -26547,7 +26597,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="747" spans="1:10">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>94</v>
       </c>
@@ -26579,7 +26629,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="748" spans="1:10">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>94</v>
       </c>
@@ -26611,7 +26661,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="749" spans="1:10">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>95</v>
       </c>
@@ -26643,7 +26693,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="750" spans="1:10">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>95</v>
       </c>
@@ -26675,7 +26725,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="751" spans="1:10">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>95</v>
       </c>
@@ -26707,7 +26757,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="752" spans="1:10">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>95</v>
       </c>
@@ -26739,7 +26789,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="753" spans="1:10">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>95</v>
       </c>
@@ -26771,7 +26821,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="754" spans="1:10">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>95</v>
       </c>
@@ -26803,7 +26853,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="755" spans="1:10">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>95</v>
       </c>
@@ -26835,7 +26885,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="756" spans="1:10">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>96</v>
       </c>
@@ -26867,7 +26917,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="757" spans="1:10">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>96</v>
       </c>
@@ -26899,7 +26949,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="758" spans="1:10">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>96</v>
       </c>
@@ -26931,7 +26981,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="759" spans="1:10">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
         <v>96</v>
       </c>
@@ -26963,7 +27013,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="760" spans="1:10">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>96</v>
       </c>
@@ -26995,7 +27045,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="761" spans="1:10">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>96</v>
       </c>
@@ -27027,7 +27077,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="762" spans="1:10">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>96</v>
       </c>
@@ -27059,7 +27109,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="763" spans="1:10">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>96</v>
       </c>
@@ -27091,7 +27141,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="764" spans="1:10">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
         <v>97</v>
       </c>
@@ -27123,7 +27173,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="765" spans="1:10">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>97</v>
       </c>
@@ -27155,7 +27205,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="766" spans="1:10">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>97</v>
       </c>
@@ -27187,7 +27237,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="767" spans="1:10">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>97</v>
       </c>
@@ -27219,7 +27269,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="768" spans="1:10">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>97</v>
       </c>
@@ -27251,7 +27301,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="769" spans="1:10">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>98</v>
       </c>
@@ -27283,7 +27333,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="770" spans="1:10">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>99</v>
       </c>
@@ -27315,7 +27365,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="771" spans="1:10">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>100</v>
       </c>
@@ -27347,7 +27397,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="772" spans="1:10">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>100</v>
       </c>
@@ -27379,7 +27429,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="773" spans="1:10">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>100</v>
       </c>
@@ -27411,7 +27461,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="774" spans="1:10">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>100</v>
       </c>
@@ -27443,7 +27493,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="775" spans="1:10">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>100</v>
       </c>
@@ -27475,7 +27525,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="776" spans="1:10">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>100</v>
       </c>
@@ -27507,7 +27557,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="777" spans="1:10">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
         <v>100</v>
       </c>
@@ -27539,7 +27589,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="778" spans="1:10">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>101</v>
       </c>
@@ -27571,7 +27621,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="779" spans="1:10">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>101</v>
       </c>
@@ -27603,7 +27653,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="780" spans="1:10">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>101</v>
       </c>
@@ -27635,7 +27685,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="781" spans="1:10">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
         <v>101</v>
       </c>
@@ -27667,7 +27717,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="782" spans="1:10">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A782" t="s">
         <v>101</v>
       </c>
@@ -27699,7 +27749,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="783" spans="1:10">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
         <v>101</v>
       </c>
@@ -27731,7 +27781,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="784" spans="1:10">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
         <v>101</v>
       </c>
@@ -27763,7 +27813,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="785" spans="1:10">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
         <v>101</v>
       </c>
@@ -27795,7 +27845,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="786" spans="1:10">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
         <v>101</v>
       </c>
@@ -27827,7 +27877,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="787" spans="1:10">
+    <row r="787" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
         <v>102</v>
       </c>
@@ -27859,7 +27909,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="788" spans="1:10">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
         <v>102</v>
       </c>
@@ -27891,7 +27941,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="789" spans="1:10">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
         <v>102</v>
       </c>
@@ -27923,7 +27973,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="790" spans="1:10">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
         <v>102</v>
       </c>
@@ -27955,7 +28005,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="791" spans="1:10">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
         <v>102</v>
       </c>
@@ -27987,7 +28037,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="792" spans="1:10">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
         <v>103</v>
       </c>
@@ -28019,7 +28069,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="793" spans="1:10">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
         <v>103</v>
       </c>
@@ -28051,7 +28101,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="794" spans="1:10">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
         <v>103</v>
       </c>
@@ -28083,7 +28133,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="795" spans="1:10">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
         <v>103</v>
       </c>
@@ -28115,7 +28165,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="796" spans="1:10">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
         <v>103</v>
       </c>
@@ -28147,7 +28197,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="797" spans="1:10">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A797" t="s">
         <v>104</v>
       </c>
@@ -28179,7 +28229,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="798" spans="1:10">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
         <v>104</v>
       </c>
@@ -28211,7 +28261,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="799" spans="1:10">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
         <v>104</v>
       </c>
@@ -28243,7 +28293,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="800" spans="1:10">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A800" t="s">
         <v>104</v>
       </c>
@@ -28275,7 +28325,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="801" spans="1:10">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A801" t="s">
         <v>104</v>
       </c>
@@ -28307,7 +28357,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="802" spans="1:10">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A802" t="s">
         <v>105</v>
       </c>
@@ -28339,7 +28389,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="803" spans="1:10">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A803" t="s">
         <v>105</v>
       </c>
@@ -28371,7 +28421,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="804" spans="1:10">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A804" t="s">
         <v>105</v>
       </c>
@@ -28403,7 +28453,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="805" spans="1:10">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A805" t="s">
         <v>105</v>
       </c>
@@ -28435,7 +28485,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="806" spans="1:10">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A806" t="s">
         <v>105</v>
       </c>
@@ -28467,7 +28517,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="807" spans="1:10">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A807" t="s">
         <v>105</v>
       </c>
@@ -28499,7 +28549,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="808" spans="1:10">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A808" t="s">
         <v>105</v>
       </c>
@@ -28531,7 +28581,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="809" spans="1:10">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A809" t="s">
         <v>105</v>
       </c>
@@ -28563,7 +28613,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="810" spans="1:10">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A810" t="s">
         <v>105</v>
       </c>
@@ -28595,7 +28645,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="811" spans="1:10">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
         <v>105</v>
       </c>
@@ -28627,7 +28677,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="812" spans="1:10">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
         <v>105</v>
       </c>
@@ -28659,7 +28709,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="813" spans="1:10">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
         <v>106</v>
       </c>
@@ -28691,7 +28741,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="814" spans="1:10">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
         <v>106</v>
       </c>
@@ -28723,7 +28773,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="815" spans="1:10">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
         <v>106</v>
       </c>
@@ -28755,7 +28805,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="816" spans="1:10">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
         <v>106</v>
       </c>
@@ -28787,7 +28837,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="817" spans="1:10">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
         <v>106</v>
       </c>
@@ -28819,7 +28869,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="818" spans="1:10">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
         <v>106</v>
       </c>
@@ -28851,7 +28901,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="819" spans="1:10">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
         <v>106</v>
       </c>
@@ -28883,7 +28933,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="820" spans="1:10">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
         <v>107</v>
       </c>
@@ -28915,7 +28965,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="821" spans="1:10">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A821" t="s">
         <v>107</v>
       </c>
@@ -28947,7 +28997,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="822" spans="1:10">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
         <v>107</v>
       </c>
@@ -28979,7 +29029,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="823" spans="1:10">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A823" t="s">
         <v>107</v>
       </c>
@@ -29011,7 +29061,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="824" spans="1:10">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A824" t="s">
         <v>107</v>
       </c>
@@ -29043,7 +29093,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="825" spans="1:10">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A825" t="s">
         <v>108</v>
       </c>
@@ -29075,7 +29125,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="826" spans="1:10">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A826" t="s">
         <v>109</v>
       </c>
@@ -29107,7 +29157,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="827" spans="1:10">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A827" t="s">
         <v>109</v>
       </c>
@@ -29139,7 +29189,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="828" spans="1:10">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A828" t="s">
         <v>109</v>
       </c>
@@ -29171,7 +29221,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="829" spans="1:10">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A829" t="s">
         <v>109</v>
       </c>
@@ -29203,7 +29253,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="830" spans="1:10">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
         <v>109</v>
       </c>
@@ -29235,7 +29285,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="831" spans="1:10">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
         <v>110</v>
       </c>
@@ -29267,7 +29317,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="832" spans="1:10">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
         <v>110</v>
       </c>
@@ -29299,7 +29349,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="833" spans="1:10">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
         <v>110</v>
       </c>
@@ -29331,7 +29381,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="834" spans="1:10">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
         <v>110</v>
       </c>
@@ -29363,7 +29413,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="835" spans="1:10">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
         <v>110</v>
       </c>
@@ -29395,7 +29445,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="836" spans="1:10">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
         <v>110</v>
       </c>
@@ -29427,7 +29477,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="837" spans="1:10">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
         <v>111</v>
       </c>
@@ -29459,7 +29509,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="838" spans="1:10">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
         <v>111</v>
       </c>
@@ -29491,7 +29541,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="839" spans="1:10">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
         <v>112</v>
       </c>
@@ -29523,7 +29573,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="840" spans="1:10">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
         <v>112</v>
       </c>
@@ -29555,7 +29605,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="841" spans="1:10">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
         <v>112</v>
       </c>
@@ -29587,7 +29637,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="842" spans="1:10">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
         <v>112</v>
       </c>
@@ -29619,7 +29669,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="843" spans="1:10">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
         <v>112</v>
       </c>
@@ -29651,7 +29701,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="844" spans="1:10">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
         <v>112</v>
       </c>
@@ -29683,7 +29733,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="845" spans="1:10">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A845" t="s">
         <v>112</v>
       </c>
@@ -29715,7 +29765,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="846" spans="1:10">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
         <v>112</v>
       </c>
@@ -29747,7 +29797,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="847" spans="1:10">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
         <v>112</v>
       </c>
@@ -29779,7 +29829,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="848" spans="1:10">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
         <v>112</v>
       </c>
@@ -29811,7 +29861,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="849" spans="1:10">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
         <v>112</v>
       </c>
@@ -29843,7 +29893,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="850" spans="1:10">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
         <v>112</v>
       </c>
@@ -29875,7 +29925,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="851" spans="1:10">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A851" t="s">
         <v>113</v>
       </c>
@@ -29907,7 +29957,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="852" spans="1:10">
+    <row r="852" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A852" t="s">
         <v>113</v>
       </c>
@@ -29939,7 +29989,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="853" spans="1:10">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A853" t="s">
         <v>113</v>
       </c>
@@ -29971,7 +30021,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="854" spans="1:10">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A854" t="s">
         <v>113</v>
       </c>
@@ -30003,7 +30053,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="855" spans="1:10">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
         <v>113</v>
       </c>
@@ -30035,7 +30085,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="856" spans="1:10">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
         <v>113</v>
       </c>
@@ -30067,7 +30117,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="857" spans="1:10">
+    <row r="857" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
         <v>113</v>
       </c>
@@ -30099,7 +30149,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="858" spans="1:10">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
         <v>113</v>
       </c>
@@ -30131,7 +30181,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="859" spans="1:10">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
         <v>113</v>
       </c>
@@ -30163,7 +30213,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="860" spans="1:10">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
         <v>113</v>
       </c>
@@ -30195,7 +30245,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="861" spans="1:10">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
         <v>113</v>
       </c>
@@ -30227,7 +30277,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="862" spans="1:10">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
         <v>113</v>
       </c>
@@ -30259,7 +30309,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="863" spans="1:10">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
         <v>113</v>
       </c>
@@ -30291,7 +30341,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="864" spans="1:10">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
         <v>113</v>
       </c>
@@ -30323,7 +30373,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="865" spans="1:10">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A865" t="s">
         <v>114</v>
       </c>
@@ -30355,7 +30405,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="866" spans="1:10">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A866" t="s">
         <v>114</v>
       </c>
@@ -30387,7 +30437,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="867" spans="1:10">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A867" t="s">
         <v>114</v>
       </c>
@@ -30419,7 +30469,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="868" spans="1:10">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A868" t="s">
         <v>114</v>
       </c>
@@ -30451,7 +30501,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="869" spans="1:10">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A869" t="s">
         <v>115</v>
       </c>
@@ -30483,7 +30533,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="870" spans="1:10">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A870" t="s">
         <v>116</v>
       </c>
@@ -30515,7 +30565,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="871" spans="1:10">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A871" t="s">
         <v>116</v>
       </c>
@@ -30547,7 +30597,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="872" spans="1:10">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A872" t="s">
         <v>116</v>
       </c>
@@ -30579,7 +30629,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="873" spans="1:10">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A873" t="s">
         <v>116</v>
       </c>
@@ -30611,7 +30661,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="874" spans="1:10">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A874" t="s">
         <v>116</v>
       </c>
@@ -30643,7 +30693,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="875" spans="1:10">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A875" t="s">
         <v>116</v>
       </c>
@@ -30675,7 +30725,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="876" spans="1:10">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A876" t="s">
         <v>116</v>
       </c>
@@ -30707,7 +30757,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="877" spans="1:10">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A877" t="s">
         <v>116</v>
       </c>
@@ -30739,7 +30789,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="878" spans="1:10">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A878" t="s">
         <v>116</v>
       </c>
@@ -30771,7 +30821,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="879" spans="1:10">
+    <row r="879" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A879" t="s">
         <v>116</v>
       </c>
@@ -30803,7 +30853,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="880" spans="1:10">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
         <v>116</v>
       </c>
@@ -30835,7 +30885,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="881" spans="1:10">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A881" t="s">
         <v>116</v>
       </c>
@@ -30867,7 +30917,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="882" spans="1:10">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
         <v>117</v>
       </c>
@@ -30899,7 +30949,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="883" spans="1:10">
+    <row r="883" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
         <v>117</v>
       </c>
@@ -30931,7 +30981,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="884" spans="1:10">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A884" t="s">
         <v>117</v>
       </c>
@@ -30963,7 +31013,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="885" spans="1:10">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A885" t="s">
         <v>117</v>
       </c>
@@ -30995,7 +31045,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="886" spans="1:10">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A886" t="s">
         <v>117</v>
       </c>
@@ -31027,7 +31077,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="887" spans="1:10">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A887" t="s">
         <v>118</v>
       </c>
@@ -31059,7 +31109,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="888" spans="1:10">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A888" t="s">
         <v>118</v>
       </c>
@@ -31091,7 +31141,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="889" spans="1:10">
+    <row r="889" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A889" t="s">
         <v>118</v>
       </c>
@@ -31123,7 +31173,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="890" spans="1:10">
+    <row r="890" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A890" t="s">
         <v>118</v>
       </c>
@@ -31155,7 +31205,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="891" spans="1:10">
+    <row r="891" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A891" t="s">
         <v>118</v>
       </c>
@@ -31187,7 +31237,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="892" spans="1:10">
+    <row r="892" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A892" t="s">
         <v>119</v>
       </c>
@@ -31219,7 +31269,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="893" spans="1:10">
+    <row r="893" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A893" t="s">
         <v>119</v>
       </c>
@@ -31251,7 +31301,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="894" spans="1:10">
+    <row r="894" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A894" t="s">
         <v>119</v>
       </c>
@@ -31283,7 +31333,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="895" spans="1:10">
+    <row r="895" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A895" t="s">
         <v>119</v>
       </c>
@@ -31315,7 +31365,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="896" spans="1:10">
+    <row r="896" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A896" t="s">
         <v>119</v>
       </c>
@@ -31347,7 +31397,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="897" spans="1:10">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A897" t="s">
         <v>119</v>
       </c>
@@ -31379,7 +31429,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="898" spans="1:10">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A898" t="s">
         <v>119</v>
       </c>
@@ -31411,7 +31461,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="899" spans="1:10">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A899" t="s">
         <v>119</v>
       </c>
@@ -31443,7 +31493,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="900" spans="1:10">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A900" t="s">
         <v>119</v>
       </c>
@@ -31475,7 +31525,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="901" spans="1:10">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A901" t="s">
         <v>119</v>
       </c>
@@ -31507,7 +31557,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="902" spans="1:10">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A902" t="s">
         <v>120</v>
       </c>
@@ -31539,7 +31589,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="903" spans="1:10">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A903" t="s">
         <v>120</v>
       </c>
@@ -31571,7 +31621,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="904" spans="1:10">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A904" t="s">
         <v>120</v>
       </c>
@@ -31603,7 +31653,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="905" spans="1:10">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A905" t="s">
         <v>120</v>
       </c>
@@ -31635,7 +31685,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="906" spans="1:10">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A906" t="s">
         <v>120</v>
       </c>
@@ -31667,7 +31717,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="907" spans="1:10">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A907" t="s">
         <v>121</v>
       </c>
@@ -31699,7 +31749,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="908" spans="1:10">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A908" t="s">
         <v>122</v>
       </c>
@@ -31731,7 +31781,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="909" spans="1:10">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A909" t="s">
         <v>123</v>
       </c>
@@ -31763,7 +31813,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="910" spans="1:10">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A910" t="s">
         <v>123</v>
       </c>
@@ -31795,7 +31845,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="911" spans="1:10">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A911" t="s">
         <v>123</v>
       </c>
@@ -31827,7 +31877,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="912" spans="1:10">
+    <row r="912" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A912" t="s">
         <v>123</v>
       </c>
@@ -31859,7 +31909,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="913" spans="1:10">
+    <row r="913" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A913" t="s">
         <v>124</v>
       </c>
@@ -31891,7 +31941,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="914" spans="1:10">
+    <row r="914" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A914" t="s">
         <v>124</v>
       </c>
@@ -31923,7 +31973,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="915" spans="1:10">
+    <row r="915" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A915" t="s">
         <v>124</v>
       </c>
@@ -31955,7 +32005,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="916" spans="1:10">
+    <row r="916" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A916" t="s">
         <v>124</v>
       </c>
@@ -31987,7 +32037,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="917" spans="1:10">
+    <row r="917" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A917" t="s">
         <v>125</v>
       </c>
@@ -32019,7 +32069,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="918" spans="1:10">
+    <row r="918" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A918" t="s">
         <v>125</v>
       </c>
@@ -32051,7 +32101,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="919" spans="1:10">
+    <row r="919" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A919" t="s">
         <v>125</v>
       </c>
@@ -32083,7 +32133,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="920" spans="1:10">
+    <row r="920" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A920" t="s">
         <v>125</v>
       </c>
@@ -32115,7 +32165,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="921" spans="1:10">
+    <row r="921" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A921" t="s">
         <v>125</v>
       </c>
@@ -32147,7 +32197,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="922" spans="1:10">
+    <row r="922" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A922" t="s">
         <v>125</v>
       </c>
@@ -32179,7 +32229,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="923" spans="1:10">
+    <row r="923" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A923" t="s">
         <v>125</v>
       </c>
@@ -32211,7 +32261,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="924" spans="1:10">
+    <row r="924" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A924" t="s">
         <v>125</v>
       </c>
@@ -32243,7 +32293,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="925" spans="1:10">
+    <row r="925" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A925" t="s">
         <v>126</v>
       </c>
@@ -32275,7 +32325,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="926" spans="1:10">
+    <row r="926" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A926" t="s">
         <v>126</v>
       </c>
@@ -32307,7 +32357,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="927" spans="1:10">
+    <row r="927" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A927" t="s">
         <v>126</v>
       </c>
@@ -32339,7 +32389,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="928" spans="1:10">
+    <row r="928" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A928" t="s">
         <v>126</v>
       </c>
@@ -32371,7 +32421,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="929" spans="1:10">
+    <row r="929" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A929" t="s">
         <v>127</v>
       </c>
@@ -32403,7 +32453,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="930" spans="1:10">
+    <row r="930" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A930" t="s">
         <v>128</v>
       </c>
@@ -32435,7 +32485,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="931" spans="1:10">
+    <row r="931" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A931" t="s">
         <v>128</v>
       </c>
@@ -32467,7 +32517,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="932" spans="1:10">
+    <row r="932" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A932" t="s">
         <v>128</v>
       </c>
@@ -32499,7 +32549,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="933" spans="1:10">
+    <row r="933" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A933" t="s">
         <v>129</v>
       </c>
@@ -32531,7 +32581,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="934" spans="1:10">
+    <row r="934" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A934" t="s">
         <v>129</v>
       </c>
@@ -32563,7 +32613,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="935" spans="1:10">
+    <row r="935" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A935" t="s">
         <v>129</v>
       </c>
@@ -32595,7 +32645,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="936" spans="1:10">
+    <row r="936" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A936" t="s">
         <v>129</v>
       </c>
@@ -32627,7 +32677,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="937" spans="1:10">
+    <row r="937" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A937" t="s">
         <v>129</v>
       </c>
@@ -32659,7 +32709,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="938" spans="1:10">
+    <row r="938" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A938" t="s">
         <v>129</v>
       </c>
@@ -32691,7 +32741,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="939" spans="1:10">
+    <row r="939" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A939" t="s">
         <v>129</v>
       </c>
@@ -32723,7 +32773,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="940" spans="1:10">
+    <row r="940" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A940" t="s">
         <v>129</v>
       </c>
@@ -32755,7 +32805,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="941" spans="1:10">
+    <row r="941" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A941" t="s">
         <v>129</v>
       </c>
@@ -32787,7 +32837,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="942" spans="1:10">
+    <row r="942" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A942" t="s">
         <v>129</v>
       </c>
@@ -32819,7 +32869,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="943" spans="1:10">
+    <row r="943" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A943" t="s">
         <v>129</v>
       </c>

--- a/pages/Sprint_Points_Men.xlsx
+++ b/pages/Sprint_Points_Men.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D1FDAC-4EF9-4E86-AE04-15ADAFB8A17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint_Points_Men" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2326,8 +2320,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2390,14 +2384,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2444,7 +2430,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2476,27 +2462,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2528,24 +2496,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2721,11 +2671,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J943"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2757,7 +2707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2789,7 +2739,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2821,7 +2771,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2853,7 +2803,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2885,7 +2835,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2917,7 +2867,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2949,7 +2899,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2981,7 +2931,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3013,7 +2963,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3045,7 +2995,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3077,7 +3027,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3109,7 +3059,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -3141,7 +3091,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3173,7 +3123,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -3205,7 +3155,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -3237,7 +3187,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -3269,7 +3219,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -3301,7 +3251,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -3333,7 +3283,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -3365,7 +3315,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -3397,7 +3347,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -3429,7 +3379,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3461,7 +3411,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3493,7 +3443,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3525,7 +3475,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3557,7 +3507,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3589,7 +3539,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3621,7 +3571,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3653,7 +3603,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3685,7 +3635,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3717,7 +3667,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -3749,7 +3699,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -3781,7 +3731,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -3813,7 +3763,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -3845,7 +3795,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -3877,7 +3827,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -3909,7 +3859,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -3941,7 +3891,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -3973,7 +3923,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -4005,7 +3955,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -4037,7 +3987,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -4069,7 +4019,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -4101,7 +4051,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -4133,7 +4083,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -4165,7 +4115,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -4197,7 +4147,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -4229,7 +4179,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -4261,7 +4211,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -4293,7 +4243,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -4325,7 +4275,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -4357,7 +4307,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -4389,7 +4339,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -4421,7 +4371,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -4453,7 +4403,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -4485,7 +4435,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -4517,7 +4467,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -4549,7 +4499,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -4581,7 +4531,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -4613,7 +4563,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -4645,7 +4595,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -4677,7 +4627,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -4709,7 +4659,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -4741,7 +4691,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -4773,7 +4723,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -4805,7 +4755,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -4837,7 +4787,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -4869,7 +4819,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -4901,7 +4851,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -4933,7 +4883,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -4965,7 +4915,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -4997,7 +4947,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -5029,7 +4979,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -5061,7 +5011,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -5093,7 +5043,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -5125,7 +5075,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -5157,7 +5107,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -5189,7 +5139,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -5221,7 +5171,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -5253,7 +5203,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -5285,7 +5235,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -5317,7 +5267,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -5349,7 +5299,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -5381,7 +5331,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -5413,7 +5363,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -5445,7 +5395,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -5477,7 +5427,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -5509,7 +5459,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -5541,7 +5491,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -5573,7 +5523,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -5605,7 +5555,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -5637,7 +5587,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -5669,7 +5619,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -5701,7 +5651,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -5733,7 +5683,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -5765,7 +5715,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -5797,7 +5747,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -5829,7 +5779,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -5861,7 +5811,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -5893,7 +5843,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -5925,7 +5875,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -5957,7 +5907,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -5989,7 +5939,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -6021,7 +5971,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -6053,7 +6003,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -6085,7 +6035,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -6117,7 +6067,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -6149,7 +6099,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -6181,7 +6131,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -6213,7 +6163,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -6245,7 +6195,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -6277,7 +6227,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -6309,7 +6259,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -6341,7 +6291,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -6373,7 +6323,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -6405,7 +6355,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -6437,7 +6387,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -6469,7 +6419,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -6501,7 +6451,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -6533,7 +6483,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -6565,7 +6515,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -6597,7 +6547,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -6629,7 +6579,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -6661,7 +6611,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -6693,7 +6643,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -6725,7 +6675,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -6757,7 +6707,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -6789,7 +6739,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -6821,7 +6771,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -6853,7 +6803,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -6885,7 +6835,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -6917,7 +6867,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -6949,7 +6899,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -6981,7 +6931,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -7013,7 +6963,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -7045,7 +6995,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10">
       <c r="A136" t="s">
         <v>20</v>
       </c>
@@ -7077,7 +7027,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -7109,7 +7059,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10">
       <c r="A138" t="s">
         <v>20</v>
       </c>
@@ -7141,7 +7091,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10">
       <c r="A139" t="s">
         <v>20</v>
       </c>
@@ -7173,7 +7123,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10">
       <c r="A140" t="s">
         <v>20</v>
       </c>
@@ -7205,7 +7155,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10">
       <c r="A141" t="s">
         <v>20</v>
       </c>
@@ -7237,7 +7187,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -7269,7 +7219,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10">
       <c r="A143" t="s">
         <v>20</v>
       </c>
@@ -7301,7 +7251,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10">
       <c r="A144" t="s">
         <v>20</v>
       </c>
@@ -7333,7 +7283,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10">
       <c r="A145" t="s">
         <v>21</v>
       </c>
@@ -7365,7 +7315,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10">
       <c r="A146" t="s">
         <v>21</v>
       </c>
@@ -7397,7 +7347,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10">
       <c r="A147" t="s">
         <v>21</v>
       </c>
@@ -7429,7 +7379,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10">
       <c r="A148" t="s">
         <v>21</v>
       </c>
@@ -7461,7 +7411,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -7493,7 +7443,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10">
       <c r="A150" t="s">
         <v>21</v>
       </c>
@@ -7525,7 +7475,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10">
       <c r="A151" t="s">
         <v>21</v>
       </c>
@@ -7557,7 +7507,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -7589,7 +7539,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10">
       <c r="A153" t="s">
         <v>21</v>
       </c>
@@ -7621,7 +7571,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10">
       <c r="A154" t="s">
         <v>21</v>
       </c>
@@ -7653,7 +7603,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -7685,7 +7635,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10">
       <c r="A156" t="s">
         <v>22</v>
       </c>
@@ -7717,7 +7667,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10">
       <c r="A157" t="s">
         <v>22</v>
       </c>
@@ -7749,7 +7699,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10">
       <c r="A158" t="s">
         <v>22</v>
       </c>
@@ -7781,7 +7731,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10">
       <c r="A159" t="s">
         <v>22</v>
       </c>
@@ -7813,7 +7763,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10">
       <c r="A160" t="s">
         <v>22</v>
       </c>
@@ -7845,7 +7795,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10">
       <c r="A161" t="s">
         <v>22</v>
       </c>
@@ -7877,7 +7827,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10">
       <c r="A162" t="s">
         <v>22</v>
       </c>
@@ -7909,7 +7859,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -7941,7 +7891,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10">
       <c r="A164" t="s">
         <v>22</v>
       </c>
@@ -7973,7 +7923,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10">
       <c r="A165" t="s">
         <v>22</v>
       </c>
@@ -8005,7 +7955,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10">
       <c r="A166" t="s">
         <v>22</v>
       </c>
@@ -8037,7 +7987,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10">
       <c r="A167" t="s">
         <v>22</v>
       </c>
@@ -8069,7 +8019,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10">
       <c r="A168" t="s">
         <v>22</v>
       </c>
@@ -8101,7 +8051,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10">
       <c r="A169" t="s">
         <v>23</v>
       </c>
@@ -8133,7 +8083,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10">
       <c r="A170" t="s">
         <v>23</v>
       </c>
@@ -8165,7 +8115,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10">
       <c r="A171" t="s">
         <v>23</v>
       </c>
@@ -8197,7 +8147,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10">
       <c r="A172" t="s">
         <v>23</v>
       </c>
@@ -8229,7 +8179,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10">
       <c r="A173" t="s">
         <v>23</v>
       </c>
@@ -8261,7 +8211,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10">
       <c r="A174" t="s">
         <v>23</v>
       </c>
@@ -8293,7 +8243,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10">
       <c r="A175" t="s">
         <v>23</v>
       </c>
@@ -8325,7 +8275,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10">
       <c r="A176" t="s">
         <v>23</v>
       </c>
@@ -8357,7 +8307,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10">
       <c r="A177" t="s">
         <v>23</v>
       </c>
@@ -8389,7 +8339,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10">
       <c r="A178" t="s">
         <v>23</v>
       </c>
@@ -8421,7 +8371,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10">
       <c r="A179" t="s">
         <v>23</v>
       </c>
@@ -8453,7 +8403,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10">
       <c r="A180" t="s">
         <v>23</v>
       </c>
@@ -8485,7 +8435,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10">
       <c r="A181" t="s">
         <v>24</v>
       </c>
@@ -8517,7 +8467,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -8549,7 +8499,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10">
       <c r="A183" t="s">
         <v>24</v>
       </c>
@@ -8581,7 +8531,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10">
       <c r="A184" t="s">
         <v>24</v>
       </c>
@@ -8613,7 +8563,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10">
       <c r="A185" t="s">
         <v>24</v>
       </c>
@@ -8645,7 +8595,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10">
       <c r="A186" t="s">
         <v>24</v>
       </c>
@@ -8677,7 +8627,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10">
       <c r="A187" t="s">
         <v>24</v>
       </c>
@@ -8709,7 +8659,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10">
       <c r="A188" t="s">
         <v>24</v>
       </c>
@@ -8741,7 +8691,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10">
       <c r="A189" t="s">
         <v>24</v>
       </c>
@@ -8773,7 +8723,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10">
       <c r="A190" t="s">
         <v>24</v>
       </c>
@@ -8805,7 +8755,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10">
       <c r="A191" t="s">
         <v>24</v>
       </c>
@@ -8837,7 +8787,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10">
       <c r="A192" t="s">
         <v>24</v>
       </c>
@@ -8869,7 +8819,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10">
       <c r="A193" t="s">
         <v>24</v>
       </c>
@@ -8901,7 +8851,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -8933,7 +8883,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10">
       <c r="A195" t="s">
         <v>24</v>
       </c>
@@ -8965,7 +8915,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10">
       <c r="A196" t="s">
         <v>25</v>
       </c>
@@ -8997,7 +8947,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10">
       <c r="A197" t="s">
         <v>25</v>
       </c>
@@ -9029,7 +8979,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10">
       <c r="A198" t="s">
         <v>25</v>
       </c>
@@ -9061,7 +9011,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10">
       <c r="A199" t="s">
         <v>25</v>
       </c>
@@ -9093,7 +9043,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10">
       <c r="A200" t="s">
         <v>25</v>
       </c>
@@ -9125,7 +9075,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10">
       <c r="A201" t="s">
         <v>25</v>
       </c>
@@ -9157,7 +9107,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10">
       <c r="A202" t="s">
         <v>25</v>
       </c>
@@ -9189,7 +9139,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:10">
       <c r="A203" t="s">
         <v>25</v>
       </c>
@@ -9221,7 +9171,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10">
       <c r="A204" t="s">
         <v>25</v>
       </c>
@@ -9253,7 +9203,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -9285,7 +9235,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -9317,7 +9267,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:10">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -9349,7 +9299,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -9381,7 +9331,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -9413,7 +9363,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -9445,7 +9395,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -9477,7 +9427,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -9509,7 +9459,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -9541,7 +9491,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -9573,7 +9523,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10">
       <c r="A215" t="s">
         <v>27</v>
       </c>
@@ -9605,7 +9555,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10">
       <c r="A216" t="s">
         <v>27</v>
       </c>
@@ -9637,7 +9587,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -9669,7 +9619,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10">
       <c r="A218" t="s">
         <v>27</v>
       </c>
@@ -9701,7 +9651,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10">
       <c r="A219" t="s">
         <v>27</v>
       </c>
@@ -9733,7 +9683,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10">
       <c r="A220" t="s">
         <v>27</v>
       </c>
@@ -9765,7 +9715,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:10">
       <c r="A221" t="s">
         <v>27</v>
       </c>
@@ -9797,7 +9747,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:10">
       <c r="A222" t="s">
         <v>28</v>
       </c>
@@ -9829,7 +9779,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:10">
       <c r="A223" t="s">
         <v>28</v>
       </c>
@@ -9861,7 +9811,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:10">
       <c r="A224" t="s">
         <v>28</v>
       </c>
@@ -9893,7 +9843,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10">
       <c r="A225" t="s">
         <v>28</v>
       </c>
@@ -9925,7 +9875,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10">
       <c r="A226" t="s">
         <v>28</v>
       </c>
@@ -9957,7 +9907,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10">
       <c r="A227" t="s">
         <v>28</v>
       </c>
@@ -9989,7 +9939,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10">
       <c r="A228" t="s">
         <v>28</v>
       </c>
@@ -10021,7 +9971,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10">
       <c r="A229" t="s">
         <v>28</v>
       </c>
@@ -10053,7 +10003,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10">
       <c r="A230" t="s">
         <v>28</v>
       </c>
@@ -10085,7 +10035,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10">
       <c r="A231" t="s">
         <v>29</v>
       </c>
@@ -10117,7 +10067,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10">
       <c r="A232" t="s">
         <v>29</v>
       </c>
@@ -10149,7 +10099,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10">
       <c r="A233" t="s">
         <v>29</v>
       </c>
@@ -10181,7 +10131,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10">
       <c r="A234" t="s">
         <v>29</v>
       </c>
@@ -10213,7 +10163,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10">
       <c r="A235" t="s">
         <v>29</v>
       </c>
@@ -10245,7 +10195,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10">
       <c r="A236" t="s">
         <v>29</v>
       </c>
@@ -10277,7 +10227,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10">
       <c r="A237" t="s">
         <v>29</v>
       </c>
@@ -10309,7 +10259,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10">
       <c r="A238" t="s">
         <v>29</v>
       </c>
@@ -10341,7 +10291,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10">
       <c r="A239" t="s">
         <v>30</v>
       </c>
@@ -10373,7 +10323,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -10405,7 +10355,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10">
       <c r="A241" t="s">
         <v>30</v>
       </c>
@@ -10437,7 +10387,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10">
       <c r="A242" t="s">
         <v>30</v>
       </c>
@@ -10469,7 +10419,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10">
       <c r="A243" t="s">
         <v>30</v>
       </c>
@@ -10501,7 +10451,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10">
       <c r="A244" t="s">
         <v>31</v>
       </c>
@@ -10533,7 +10483,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10">
       <c r="A245" t="s">
         <v>31</v>
       </c>
@@ -10565,7 +10515,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10">
       <c r="A246" t="s">
         <v>31</v>
       </c>
@@ -10597,7 +10547,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10">
       <c r="A247" t="s">
         <v>31</v>
       </c>
@@ -10629,7 +10579,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10">
       <c r="A248" t="s">
         <v>31</v>
       </c>
@@ -10661,7 +10611,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10">
       <c r="A249" t="s">
         <v>31</v>
       </c>
@@ -10693,7 +10643,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10">
       <c r="A250" t="s">
         <v>31</v>
       </c>
@@ -10725,7 +10675,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10">
       <c r="A251" t="s">
         <v>31</v>
       </c>
@@ -10757,7 +10707,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10">
       <c r="A252" t="s">
         <v>31</v>
       </c>
@@ -10789,7 +10739,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10">
       <c r="A253" t="s">
         <v>31</v>
       </c>
@@ -10821,7 +10771,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10">
       <c r="A254" t="s">
         <v>31</v>
       </c>
@@ -10853,7 +10803,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10">
       <c r="A255" t="s">
         <v>31</v>
       </c>
@@ -10885,7 +10835,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10">
       <c r="A256" t="s">
         <v>31</v>
       </c>
@@ -10917,7 +10867,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10">
       <c r="A257" t="s">
         <v>31</v>
       </c>
@@ -10949,7 +10899,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10">
       <c r="A258" t="s">
         <v>31</v>
       </c>
@@ -10981,7 +10931,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10">
       <c r="A259" t="s">
         <v>31</v>
       </c>
@@ -11013,7 +10963,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10">
       <c r="A260" t="s">
         <v>32</v>
       </c>
@@ -11045,7 +10995,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10">
       <c r="A261" t="s">
         <v>32</v>
       </c>
@@ -11077,7 +11027,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10">
       <c r="A262" t="s">
         <v>32</v>
       </c>
@@ -11109,7 +11059,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10">
       <c r="A263" t="s">
         <v>32</v>
       </c>
@@ -11141,7 +11091,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10">
       <c r="A264" t="s">
         <v>32</v>
       </c>
@@ -11173,7 +11123,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10">
       <c r="A265" t="s">
         <v>32</v>
       </c>
@@ -11205,7 +11155,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10">
       <c r="A266" t="s">
         <v>32</v>
       </c>
@@ -11237,7 +11187,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10">
       <c r="A267" t="s">
         <v>32</v>
       </c>
@@ -11269,7 +11219,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10">
       <c r="A268" t="s">
         <v>32</v>
       </c>
@@ -11301,7 +11251,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10">
       <c r="A269" t="s">
         <v>32</v>
       </c>
@@ -11333,7 +11283,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10">
       <c r="A270" t="s">
         <v>32</v>
       </c>
@@ -11365,7 +11315,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10">
       <c r="A271" t="s">
         <v>32</v>
       </c>
@@ -11397,7 +11347,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10">
       <c r="A272" t="s">
         <v>32</v>
       </c>
@@ -11429,7 +11379,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>33</v>
       </c>
@@ -11461,7 +11411,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>33</v>
       </c>
@@ -11493,7 +11443,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>33</v>
       </c>
@@ -11525,7 +11475,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>33</v>
       </c>
@@ -11557,7 +11507,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>33</v>
       </c>
@@ -11589,7 +11539,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10">
       <c r="A278" t="s">
         <v>33</v>
       </c>
@@ -11621,7 +11571,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10">
       <c r="A279" t="s">
         <v>33</v>
       </c>
@@ -11653,7 +11603,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10">
       <c r="A280" t="s">
         <v>33</v>
       </c>
@@ -11685,7 +11635,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10">
       <c r="A281" t="s">
         <v>33</v>
       </c>
@@ -11717,7 +11667,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10">
       <c r="A282" t="s">
         <v>33</v>
       </c>
@@ -11749,7 +11699,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10">
       <c r="A283" t="s">
         <v>33</v>
       </c>
@@ -11781,7 +11731,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10">
       <c r="A284" t="s">
         <v>33</v>
       </c>
@@ -11813,7 +11763,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10">
       <c r="A285" t="s">
         <v>33</v>
       </c>
@@ -11845,7 +11795,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10">
       <c r="A286" t="s">
         <v>33</v>
       </c>
@@ -11877,7 +11827,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10">
       <c r="A287" t="s">
         <v>34</v>
       </c>
@@ -11909,7 +11859,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10">
       <c r="A288" t="s">
         <v>34</v>
       </c>
@@ -11941,7 +11891,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10">
       <c r="A289" t="s">
         <v>34</v>
       </c>
@@ -11973,7 +11923,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10">
       <c r="A290" t="s">
         <v>34</v>
       </c>
@@ -12005,7 +11955,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10">
       <c r="A291" t="s">
         <v>34</v>
       </c>
@@ -12037,7 +11987,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10">
       <c r="A292" t="s">
         <v>34</v>
       </c>
@@ -12069,7 +12019,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10">
       <c r="A293" t="s">
         <v>34</v>
       </c>
@@ -12101,7 +12051,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10">
       <c r="A294" t="s">
         <v>35</v>
       </c>
@@ -12133,7 +12083,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10">
       <c r="A295" t="s">
         <v>35</v>
       </c>
@@ -12165,7 +12115,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10">
       <c r="A296" t="s">
         <v>35</v>
       </c>
@@ -12197,7 +12147,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10">
       <c r="A297" t="s">
         <v>35</v>
       </c>
@@ -12229,7 +12179,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10">
       <c r="A298" t="s">
         <v>35</v>
       </c>
@@ -12261,7 +12211,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10">
       <c r="A299" t="s">
         <v>35</v>
       </c>
@@ -12293,7 +12243,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10">
       <c r="A300" t="s">
         <v>35</v>
       </c>
@@ -12325,7 +12275,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10">
       <c r="A301" t="s">
         <v>35</v>
       </c>
@@ -12357,7 +12307,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10">
       <c r="A302" t="s">
         <v>35</v>
       </c>
@@ -12389,7 +12339,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10">
       <c r="A303" t="s">
         <v>35</v>
       </c>
@@ -12421,7 +12371,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10">
       <c r="A304" t="s">
         <v>35</v>
       </c>
@@ -12453,7 +12403,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10">
       <c r="A305" t="s">
         <v>35</v>
       </c>
@@ -12485,7 +12435,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10">
       <c r="A306" t="s">
         <v>35</v>
       </c>
@@ -12517,7 +12467,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10">
       <c r="A307" t="s">
         <v>35</v>
       </c>
@@ -12549,7 +12499,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10">
       <c r="A308" t="s">
         <v>36</v>
       </c>
@@ -12581,7 +12531,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10">
       <c r="A309" t="s">
         <v>36</v>
       </c>
@@ -12613,7 +12563,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10">
       <c r="A310" t="s">
         <v>36</v>
       </c>
@@ -12645,7 +12595,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10">
       <c r="A311" t="s">
         <v>36</v>
       </c>
@@ -12677,7 +12627,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10">
       <c r="A312" t="s">
         <v>36</v>
       </c>
@@ -12709,7 +12659,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10">
       <c r="A313" t="s">
         <v>36</v>
       </c>
@@ -12741,7 +12691,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10">
       <c r="A314" t="s">
         <v>36</v>
       </c>
@@ -12773,7 +12723,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10">
       <c r="A315" t="s">
         <v>37</v>
       </c>
@@ -12805,7 +12755,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10">
       <c r="A316" t="s">
         <v>37</v>
       </c>
@@ -12837,7 +12787,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10">
       <c r="A317" t="s">
         <v>37</v>
       </c>
@@ -12869,7 +12819,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10">
       <c r="A318" t="s">
         <v>37</v>
       </c>
@@ -12901,7 +12851,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10">
       <c r="A319" t="s">
         <v>37</v>
       </c>
@@ -12933,7 +12883,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10">
       <c r="A320" t="s">
         <v>37</v>
       </c>
@@ -12965,7 +12915,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10">
       <c r="A321" t="s">
         <v>37</v>
       </c>
@@ -12997,7 +12947,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10">
       <c r="A322" t="s">
         <v>37</v>
       </c>
@@ -13029,7 +12979,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10">
       <c r="A323" t="s">
         <v>37</v>
       </c>
@@ -13061,7 +13011,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10">
       <c r="A324" t="s">
         <v>37</v>
       </c>
@@ -13093,7 +13043,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10">
       <c r="A325" t="s">
         <v>37</v>
       </c>
@@ -13125,7 +13075,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10">
       <c r="A326" t="s">
         <v>37</v>
       </c>
@@ -13157,7 +13107,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10">
       <c r="A327" t="s">
         <v>37</v>
       </c>
@@ -13189,7 +13139,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10">
       <c r="A328" t="s">
         <v>37</v>
       </c>
@@ -13221,7 +13171,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10">
       <c r="A329" t="s">
         <v>37</v>
       </c>
@@ -13253,7 +13203,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10">
       <c r="A330" t="s">
         <v>37</v>
       </c>
@@ -13285,7 +13235,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10">
       <c r="A331" t="s">
         <v>37</v>
       </c>
@@ -13317,7 +13267,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10">
       <c r="A332" t="s">
         <v>37</v>
       </c>
@@ -13349,7 +13299,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10">
       <c r="A333" t="s">
         <v>38</v>
       </c>
@@ -13381,7 +13331,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10">
       <c r="A334" t="s">
         <v>38</v>
       </c>
@@ -13413,7 +13363,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10">
       <c r="A335" t="s">
         <v>38</v>
       </c>
@@ -13445,7 +13395,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10">
       <c r="A336" t="s">
         <v>38</v>
       </c>
@@ -13477,7 +13427,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10">
       <c r="A337" t="s">
         <v>38</v>
       </c>
@@ -13509,7 +13459,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10">
       <c r="A338" t="s">
         <v>38</v>
       </c>
@@ -13541,7 +13491,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:10">
       <c r="A339" t="s">
         <v>38</v>
       </c>
@@ -13573,7 +13523,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10">
       <c r="A340" t="s">
         <v>38</v>
       </c>
@@ -13605,7 +13555,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:10">
       <c r="A341" t="s">
         <v>38</v>
       </c>
@@ -13637,7 +13587,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:10">
       <c r="A342" t="s">
         <v>39</v>
       </c>
@@ -13669,7 +13619,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10">
       <c r="A343" t="s">
         <v>39</v>
       </c>
@@ -13701,7 +13651,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:10">
       <c r="A344" t="s">
         <v>39</v>
       </c>
@@ -13733,7 +13683,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10">
       <c r="A345" t="s">
         <v>39</v>
       </c>
@@ -13765,7 +13715,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10">
       <c r="A346" t="s">
         <v>39</v>
       </c>
@@ -13797,7 +13747,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:10">
       <c r="A347" t="s">
         <v>39</v>
       </c>
@@ -13829,7 +13779,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10">
       <c r="A348" t="s">
         <v>39</v>
       </c>
@@ -13861,7 +13811,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10">
       <c r="A349" t="s">
         <v>39</v>
       </c>
@@ -13893,7 +13843,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10">
       <c r="A350" t="s">
         <v>40</v>
       </c>
@@ -13925,7 +13875,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:10">
       <c r="A351" t="s">
         <v>40</v>
       </c>
@@ -13957,7 +13907,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10">
       <c r="A352" t="s">
         <v>40</v>
       </c>
@@ -13989,7 +13939,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10">
       <c r="A353" t="s">
         <v>40</v>
       </c>
@@ -14021,7 +13971,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:10">
       <c r="A354" t="s">
         <v>40</v>
       </c>
@@ -14053,7 +14003,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10">
       <c r="A355" t="s">
         <v>40</v>
       </c>
@@ -14085,7 +14035,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10">
       <c r="A356" t="s">
         <v>40</v>
       </c>
@@ -14117,7 +14067,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10">
       <c r="A357" t="s">
         <v>40</v>
       </c>
@@ -14149,7 +14099,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10">
       <c r="A358" t="s">
         <v>41</v>
       </c>
@@ -14181,7 +14131,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10">
       <c r="A359" t="s">
         <v>41</v>
       </c>
@@ -14213,7 +14163,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10">
       <c r="A360" t="s">
         <v>41</v>
       </c>
@@ -14245,7 +14195,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10">
       <c r="A361" t="s">
         <v>41</v>
       </c>
@@ -14277,7 +14227,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10">
       <c r="A362" t="s">
         <v>41</v>
       </c>
@@ -14309,7 +14259,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10">
       <c r="A363" t="s">
         <v>41</v>
       </c>
@@ -14341,7 +14291,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10">
       <c r="A364" t="s">
         <v>41</v>
       </c>
@@ -14373,7 +14323,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10">
       <c r="A365" t="s">
         <v>41</v>
       </c>
@@ -14405,7 +14355,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10">
       <c r="A366" t="s">
         <v>41</v>
       </c>
@@ -14437,7 +14387,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10">
       <c r="A367" t="s">
         <v>41</v>
       </c>
@@ -14469,7 +14419,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10">
       <c r="A368" t="s">
         <v>41</v>
       </c>
@@ -14501,7 +14451,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10">
       <c r="A369" t="s">
         <v>42</v>
       </c>
@@ -14533,7 +14483,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10">
       <c r="A370" t="s">
         <v>42</v>
       </c>
@@ -14565,7 +14515,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10">
       <c r="A371" t="s">
         <v>42</v>
       </c>
@@ -14597,7 +14547,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10">
       <c r="A372" t="s">
         <v>42</v>
       </c>
@@ -14629,7 +14579,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10">
       <c r="A373" t="s">
         <v>42</v>
       </c>
@@ -14661,7 +14611,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10">
       <c r="A374" t="s">
         <v>42</v>
       </c>
@@ -14693,7 +14643,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10">
       <c r="A375" t="s">
         <v>42</v>
       </c>
@@ -14725,7 +14675,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10">
       <c r="A376" t="s">
         <v>42</v>
       </c>
@@ -14757,7 +14707,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10">
       <c r="A377" t="s">
         <v>43</v>
       </c>
@@ -14789,7 +14739,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:10">
       <c r="A378" t="s">
         <v>43</v>
       </c>
@@ -14821,7 +14771,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:10">
       <c r="A379" t="s">
         <v>43</v>
       </c>
@@ -14853,7 +14803,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:10">
       <c r="A380" t="s">
         <v>43</v>
       </c>
@@ -14885,7 +14835,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:10">
       <c r="A381" t="s">
         <v>43</v>
       </c>
@@ -14917,7 +14867,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10">
       <c r="A382" t="s">
         <v>43</v>
       </c>
@@ -14949,7 +14899,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10">
       <c r="A383" t="s">
         <v>43</v>
       </c>
@@ -14981,7 +14931,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10">
       <c r="A384" t="s">
         <v>43</v>
       </c>
@@ -15013,7 +14963,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10">
       <c r="A385" t="s">
         <v>43</v>
       </c>
@@ -15045,7 +14995,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:10">
       <c r="A386" t="s">
         <v>43</v>
       </c>
@@ -15077,7 +15027,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10">
       <c r="A387" t="s">
         <v>43</v>
       </c>
@@ -15109,7 +15059,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:10">
       <c r="A388" t="s">
         <v>43</v>
       </c>
@@ -15141,7 +15091,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:10">
       <c r="A389" t="s">
         <v>44</v>
       </c>
@@ -15173,7 +15123,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:10">
       <c r="A390" t="s">
         <v>44</v>
       </c>
@@ -15205,7 +15155,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:10">
       <c r="A391" t="s">
         <v>44</v>
       </c>
@@ -15237,7 +15187,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:10">
       <c r="A392" t="s">
         <v>44</v>
       </c>
@@ -15269,7 +15219,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:10">
       <c r="A393" t="s">
         <v>44</v>
       </c>
@@ -15301,7 +15251,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:10">
       <c r="A394" t="s">
         <v>44</v>
       </c>
@@ -15333,7 +15283,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:10">
       <c r="A395" t="s">
         <v>44</v>
       </c>
@@ -15365,7 +15315,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:10">
       <c r="A396" t="s">
         <v>45</v>
       </c>
@@ -15397,7 +15347,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:10">
       <c r="A397" t="s">
         <v>45</v>
       </c>
@@ -15429,7 +15379,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:10">
       <c r="A398" t="s">
         <v>45</v>
       </c>
@@ -15461,7 +15411,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:10">
       <c r="A399" t="s">
         <v>45</v>
       </c>
@@ -15493,7 +15443,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:10">
       <c r="A400" t="s">
         <v>45</v>
       </c>
@@ -15525,7 +15475,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:10">
       <c r="A401" t="s">
         <v>45</v>
       </c>
@@ -15557,7 +15507,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:10">
       <c r="A402" t="s">
         <v>45</v>
       </c>
@@ -15589,7 +15539,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:10">
       <c r="A403" t="s">
         <v>45</v>
       </c>
@@ -15621,7 +15571,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:10">
       <c r="A404" t="s">
         <v>45</v>
       </c>
@@ -15653,7 +15603,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:10">
       <c r="A405" t="s">
         <v>45</v>
       </c>
@@ -15685,7 +15635,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:10">
       <c r="A406" t="s">
         <v>45</v>
       </c>
@@ -15717,7 +15667,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:10">
       <c r="A407" t="s">
         <v>45</v>
       </c>
@@ -15749,7 +15699,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:10">
       <c r="A408" t="s">
         <v>45</v>
       </c>
@@ -15781,7 +15731,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:10">
       <c r="A409" t="s">
         <v>45</v>
       </c>
@@ -15813,7 +15763,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:10">
       <c r="A410" t="s">
         <v>45</v>
       </c>
@@ -15845,7 +15795,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:10">
       <c r="A411" t="s">
         <v>46</v>
       </c>
@@ -15877,7 +15827,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:10">
       <c r="A412" t="s">
         <v>46</v>
       </c>
@@ -15909,7 +15859,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:10">
       <c r="A413" t="s">
         <v>46</v>
       </c>
@@ -15941,7 +15891,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:10">
       <c r="A414" t="s">
         <v>46</v>
       </c>
@@ -15973,7 +15923,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:10">
       <c r="A415" t="s">
         <v>46</v>
       </c>
@@ -16005,7 +15955,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:10">
       <c r="A416" t="s">
         <v>46</v>
       </c>
@@ -16037,7 +15987,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10">
       <c r="A417" t="s">
         <v>46</v>
       </c>
@@ -16069,7 +16019,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10">
       <c r="A418" t="s">
         <v>46</v>
       </c>
@@ -16101,7 +16051,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10">
       <c r="A419" t="s">
         <v>47</v>
       </c>
@@ -16133,7 +16083,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10">
       <c r="A420" t="s">
         <v>47</v>
       </c>
@@ -16165,7 +16115,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10">
       <c r="A421" t="s">
         <v>47</v>
       </c>
@@ -16197,7 +16147,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10">
       <c r="A422" t="s">
         <v>47</v>
       </c>
@@ -16229,7 +16179,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:10">
       <c r="A423" t="s">
         <v>47</v>
       </c>
@@ -16261,7 +16211,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:10">
       <c r="A424" t="s">
         <v>47</v>
       </c>
@@ -16293,7 +16243,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10">
       <c r="A425" t="s">
         <v>47</v>
       </c>
@@ -16325,7 +16275,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:10">
       <c r="A426" t="s">
         <v>47</v>
       </c>
@@ -16357,7 +16307,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:10">
       <c r="A427" t="s">
         <v>47</v>
       </c>
@@ -16389,7 +16339,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10">
       <c r="A428" t="s">
         <v>47</v>
       </c>
@@ -16421,7 +16371,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:10">
       <c r="A429" t="s">
         <v>47</v>
       </c>
@@ -16453,7 +16403,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10">
       <c r="A430" t="s">
         <v>48</v>
       </c>
@@ -16485,7 +16435,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:10">
       <c r="A431" t="s">
         <v>48</v>
       </c>
@@ -16517,7 +16467,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:10">
       <c r="A432" t="s">
         <v>48</v>
       </c>
@@ -16549,7 +16499,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:10">
       <c r="A433" t="s">
         <v>48</v>
       </c>
@@ -16581,7 +16531,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:10">
       <c r="A434" t="s">
         <v>48</v>
       </c>
@@ -16613,7 +16563,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:10">
       <c r="A435" t="s">
         <v>48</v>
       </c>
@@ -16645,7 +16595,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:10">
       <c r="A436" t="s">
         <v>48</v>
       </c>
@@ -16677,7 +16627,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:10">
       <c r="A437" t="s">
         <v>48</v>
       </c>
@@ -16709,7 +16659,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:10">
       <c r="A438" t="s">
         <v>48</v>
       </c>
@@ -16741,7 +16691,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:10">
       <c r="A439" t="s">
         <v>48</v>
       </c>
@@ -16773,7 +16723,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:10">
       <c r="A440" t="s">
         <v>48</v>
       </c>
@@ -16805,7 +16755,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:10">
       <c r="A441" t="s">
         <v>49</v>
       </c>
@@ -16837,7 +16787,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:10">
       <c r="A442" t="s">
         <v>49</v>
       </c>
@@ -16869,7 +16819,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:10">
       <c r="A443" t="s">
         <v>49</v>
       </c>
@@ -16901,7 +16851,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:10">
       <c r="A444" t="s">
         <v>49</v>
       </c>
@@ -16933,7 +16883,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:10">
       <c r="A445" t="s">
         <v>49</v>
       </c>
@@ -16965,7 +16915,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:10">
       <c r="A446" t="s">
         <v>49</v>
       </c>
@@ -16997,7 +16947,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:10">
       <c r="A447" t="s">
         <v>49</v>
       </c>
@@ -17029,7 +16979,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:10">
       <c r="A448" t="s">
         <v>49</v>
       </c>
@@ -17061,7 +17011,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:10">
       <c r="A449" t="s">
         <v>49</v>
       </c>
@@ -17093,7 +17043,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:10">
       <c r="A450" t="s">
         <v>49</v>
       </c>
@@ -17125,7 +17075,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:10">
       <c r="A451" t="s">
         <v>49</v>
       </c>
@@ -17157,7 +17107,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:10">
       <c r="A452" t="s">
         <v>49</v>
       </c>
@@ -17189,7 +17139,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:10">
       <c r="A453" t="s">
         <v>49</v>
       </c>
@@ -17221,7 +17171,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:10">
       <c r="A454" t="s">
         <v>49</v>
       </c>
@@ -17253,7 +17203,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:10">
       <c r="A455" t="s">
         <v>49</v>
       </c>
@@ -17285,7 +17235,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:10">
       <c r="A456" t="s">
         <v>50</v>
       </c>
@@ -17317,7 +17267,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:10">
       <c r="A457" t="s">
         <v>50</v>
       </c>
@@ -17349,7 +17299,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:10">
       <c r="A458" t="s">
         <v>50</v>
       </c>
@@ -17381,7 +17331,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:10">
       <c r="A459" t="s">
         <v>50</v>
       </c>
@@ -17413,7 +17363,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:10">
       <c r="A460" t="s">
         <v>50</v>
       </c>
@@ -17445,7 +17395,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:10">
       <c r="A461" t="s">
         <v>50</v>
       </c>
@@ -17477,7 +17427,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:10">
       <c r="A462" t="s">
         <v>50</v>
       </c>
@@ -17509,7 +17459,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:10">
       <c r="A463" t="s">
         <v>50</v>
       </c>
@@ -17541,7 +17491,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:10">
       <c r="A464" t="s">
         <v>50</v>
       </c>
@@ -17573,7 +17523,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:10">
       <c r="A465" t="s">
         <v>50</v>
       </c>
@@ -17605,7 +17555,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:10">
       <c r="A466" t="s">
         <v>50</v>
       </c>
@@ -17637,7 +17587,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10">
       <c r="A467" t="s">
         <v>50</v>
       </c>
@@ -17669,7 +17619,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10">
       <c r="A468" t="s">
         <v>51</v>
       </c>
@@ -17701,7 +17651,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10">
       <c r="A469" t="s">
         <v>51</v>
       </c>
@@ -17733,7 +17683,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10">
       <c r="A470" t="s">
         <v>51</v>
       </c>
@@ -17765,7 +17715,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10">
       <c r="A471" t="s">
         <v>51</v>
       </c>
@@ -17797,7 +17747,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10">
       <c r="A472" t="s">
         <v>51</v>
       </c>
@@ -17829,7 +17779,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:10">
       <c r="A473" t="s">
         <v>51</v>
       </c>
@@ -17861,7 +17811,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:10">
       <c r="A474" t="s">
         <v>51</v>
       </c>
@@ -17893,7 +17843,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:10">
       <c r="A475" t="s">
         <v>51</v>
       </c>
@@ -17925,7 +17875,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10">
       <c r="A476" t="s">
         <v>51</v>
       </c>
@@ -17957,7 +17907,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10">
       <c r="A477" t="s">
         <v>51</v>
       </c>
@@ -17989,7 +17939,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10">
       <c r="A478" t="s">
         <v>52</v>
       </c>
@@ -18021,7 +17971,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10">
       <c r="A479" t="s">
         <v>52</v>
       </c>
@@ -18053,7 +18003,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10">
       <c r="A480" t="s">
         <v>52</v>
       </c>
@@ -18085,7 +18035,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:10">
       <c r="A481" t="s">
         <v>52</v>
       </c>
@@ -18117,7 +18067,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:10">
       <c r="A482" t="s">
         <v>52</v>
       </c>
@@ -18149,7 +18099,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:10">
       <c r="A483" t="s">
         <v>52</v>
       </c>
@@ -18181,7 +18131,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:10">
       <c r="A484" t="s">
         <v>52</v>
       </c>
@@ -18213,7 +18163,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:10">
       <c r="A485" t="s">
         <v>52</v>
       </c>
@@ -18245,7 +18195,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:10">
       <c r="A486" t="s">
         <v>52</v>
       </c>
@@ -18277,7 +18227,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:10">
       <c r="A487" t="s">
         <v>53</v>
       </c>
@@ -18309,7 +18259,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:10">
       <c r="A488" t="s">
         <v>53</v>
       </c>
@@ -18341,7 +18291,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:10">
       <c r="A489" t="s">
         <v>53</v>
       </c>
@@ -18373,7 +18323,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:10">
       <c r="A490" t="s">
         <v>53</v>
       </c>
@@ -18405,7 +18355,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:10">
       <c r="A491" t="s">
         <v>53</v>
       </c>
@@ -18437,7 +18387,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:10">
       <c r="A492" t="s">
         <v>53</v>
       </c>
@@ -18469,7 +18419,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:10">
       <c r="A493" t="s">
         <v>53</v>
       </c>
@@ -18501,7 +18451,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:10">
       <c r="A494" t="s">
         <v>53</v>
       </c>
@@ -18533,7 +18483,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:10">
       <c r="A495" t="s">
         <v>53</v>
       </c>
@@ -18565,7 +18515,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:10">
       <c r="A496" t="s">
         <v>54</v>
       </c>
@@ -18597,7 +18547,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:10">
       <c r="A497" t="s">
         <v>54</v>
       </c>
@@ -18629,7 +18579,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:10">
       <c r="A498" t="s">
         <v>54</v>
       </c>
@@ -18661,7 +18611,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:10">
       <c r="A499" t="s">
         <v>54</v>
       </c>
@@ -18693,7 +18643,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:10">
       <c r="A500" t="s">
         <v>54</v>
       </c>
@@ -18725,7 +18675,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:10">
       <c r="A501" t="s">
         <v>54</v>
       </c>
@@ -18757,7 +18707,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:10">
       <c r="A502" t="s">
         <v>54</v>
       </c>
@@ -18789,7 +18739,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:10">
       <c r="A503" t="s">
         <v>54</v>
       </c>
@@ -18821,7 +18771,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:10">
       <c r="A504" t="s">
         <v>55</v>
       </c>
@@ -18853,7 +18803,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:10">
       <c r="A505" t="s">
         <v>55</v>
       </c>
@@ -18885,7 +18835,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:10">
       <c r="A506" t="s">
         <v>55</v>
       </c>
@@ -18917,7 +18867,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:10">
       <c r="A507" t="s">
         <v>55</v>
       </c>
@@ -18949,7 +18899,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:10">
       <c r="A508" t="s">
         <v>55</v>
       </c>
@@ -18981,7 +18931,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:10">
       <c r="A509" t="s">
         <v>55</v>
       </c>
@@ -19013,7 +18963,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:10">
       <c r="A510" t="s">
         <v>55</v>
       </c>
@@ -19045,7 +18995,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:10">
       <c r="A511" t="s">
         <v>56</v>
       </c>
@@ -19077,7 +19027,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:10">
       <c r="A512" t="s">
         <v>56</v>
       </c>
@@ -19109,7 +19059,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:10">
       <c r="A513" t="s">
         <v>56</v>
       </c>
@@ -19141,7 +19091,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:10">
       <c r="A514" t="s">
         <v>56</v>
       </c>
@@ -19173,7 +19123,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:10">
       <c r="A515" t="s">
         <v>56</v>
       </c>
@@ -19205,7 +19155,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:10">
       <c r="A516" t="s">
         <v>56</v>
       </c>
@@ -19237,7 +19187,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:10">
       <c r="A517" t="s">
         <v>56</v>
       </c>
@@ -19269,7 +19219,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:10">
       <c r="A518" t="s">
         <v>57</v>
       </c>
@@ -19301,7 +19251,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:10">
       <c r="A519" t="s">
         <v>57</v>
       </c>
@@ -19333,7 +19283,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:10">
       <c r="A520" t="s">
         <v>57</v>
       </c>
@@ -19365,7 +19315,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:10">
       <c r="A521" t="s">
         <v>57</v>
       </c>
@@ -19397,7 +19347,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:10">
       <c r="A522" t="s">
         <v>57</v>
       </c>
@@ -19429,7 +19379,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:10">
       <c r="A523" t="s">
         <v>57</v>
       </c>
@@ -19461,7 +19411,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:10">
       <c r="A524" t="s">
         <v>57</v>
       </c>
@@ -19493,7 +19443,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:10">
       <c r="A525" t="s">
         <v>57</v>
       </c>
@@ -19525,7 +19475,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:10">
       <c r="A526" t="s">
         <v>57</v>
       </c>
@@ -19557,7 +19507,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:10">
       <c r="A527" t="s">
         <v>57</v>
       </c>
@@ -19589,7 +19539,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:10">
       <c r="A528" t="s">
         <v>57</v>
       </c>
@@ -19621,7 +19571,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:10">
       <c r="A529" t="s">
         <v>57</v>
       </c>
@@ -19653,7 +19603,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:10">
       <c r="A530" t="s">
         <v>57</v>
       </c>
@@ -19685,7 +19635,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:10">
       <c r="A531" t="s">
         <v>57</v>
       </c>
@@ -19717,7 +19667,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:10">
       <c r="A532" t="s">
         <v>57</v>
       </c>
@@ -19749,7 +19699,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:10">
       <c r="A533" t="s">
         <v>58</v>
       </c>
@@ -19781,7 +19731,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:10">
       <c r="A534" t="s">
         <v>58</v>
       </c>
@@ -19813,7 +19763,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:10">
       <c r="A535" t="s">
         <v>58</v>
       </c>
@@ -19845,7 +19795,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:10">
       <c r="A536" t="s">
         <v>58</v>
       </c>
@@ -19877,7 +19827,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:10">
       <c r="A537" t="s">
         <v>58</v>
       </c>
@@ -19909,7 +19859,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:10">
       <c r="A538" t="s">
         <v>58</v>
       </c>
@@ -19941,7 +19891,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:10">
       <c r="A539" t="s">
         <v>58</v>
       </c>
@@ -19973,7 +19923,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:10">
       <c r="A540" t="s">
         <v>58</v>
       </c>
@@ -20005,7 +19955,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:10">
       <c r="A541" t="s">
         <v>58</v>
       </c>
@@ -20037,7 +19987,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:10">
       <c r="A542" t="s">
         <v>59</v>
       </c>
@@ -20069,7 +20019,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:10">
       <c r="A543" t="s">
         <v>59</v>
       </c>
@@ -20101,7 +20051,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:10">
       <c r="A544" t="s">
         <v>59</v>
       </c>
@@ -20133,7 +20083,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:10">
       <c r="A545" t="s">
         <v>59</v>
       </c>
@@ -20165,7 +20115,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:10">
       <c r="A546" t="s">
         <v>60</v>
       </c>
@@ -20197,7 +20147,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:10">
       <c r="A547" t="s">
         <v>60</v>
       </c>
@@ -20229,7 +20179,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:10">
       <c r="A548" t="s">
         <v>60</v>
       </c>
@@ -20261,7 +20211,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:10">
       <c r="A549" t="s">
         <v>60</v>
       </c>
@@ -20293,7 +20243,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:10">
       <c r="A550" t="s">
         <v>60</v>
       </c>
@@ -20325,7 +20275,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:10">
       <c r="A551" t="s">
         <v>60</v>
       </c>
@@ -20357,7 +20307,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:10">
       <c r="A552" t="s">
         <v>60</v>
       </c>
@@ -20389,7 +20339,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:10">
       <c r="A553" t="s">
         <v>61</v>
       </c>
@@ -20421,7 +20371,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:10">
       <c r="A554" t="s">
         <v>61</v>
       </c>
@@ -20453,7 +20403,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:10">
       <c r="A555" t="s">
         <v>61</v>
       </c>
@@ -20485,7 +20435,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:10">
       <c r="A556" t="s">
         <v>61</v>
       </c>
@@ -20517,7 +20467,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:10">
       <c r="A557" t="s">
         <v>61</v>
       </c>
@@ -20549,7 +20499,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:10">
       <c r="A558" t="s">
         <v>61</v>
       </c>
@@ -20581,7 +20531,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:10">
       <c r="A559" t="s">
         <v>61</v>
       </c>
@@ -20613,7 +20563,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:10">
       <c r="A560" t="s">
         <v>62</v>
       </c>
@@ -20645,7 +20595,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:10">
       <c r="A561" t="s">
         <v>62</v>
       </c>
@@ -20677,7 +20627,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:10">
       <c r="A562" t="s">
         <v>62</v>
       </c>
@@ -20709,7 +20659,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:10">
       <c r="A563" t="s">
         <v>62</v>
       </c>
@@ -20741,7 +20691,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:10">
       <c r="A564" t="s">
         <v>63</v>
       </c>
@@ -20773,7 +20723,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:10">
       <c r="A565" t="s">
         <v>63</v>
       </c>
@@ -20805,7 +20755,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:10">
       <c r="A566" t="s">
         <v>63</v>
       </c>
@@ -20837,7 +20787,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:10">
       <c r="A567" t="s">
         <v>63</v>
       </c>
@@ -20869,7 +20819,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:10">
       <c r="A568" t="s">
         <v>64</v>
       </c>
@@ -20901,7 +20851,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:10">
       <c r="A569" t="s">
         <v>64</v>
       </c>
@@ -20933,7 +20883,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:10">
       <c r="A570" t="s">
         <v>64</v>
       </c>
@@ -20965,7 +20915,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:10">
       <c r="A571" t="s">
         <v>64</v>
       </c>
@@ -20997,7 +20947,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:10">
       <c r="A572" t="s">
         <v>64</v>
       </c>
@@ -21029,7 +20979,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:10">
       <c r="A573" t="s">
         <v>64</v>
       </c>
@@ -21061,7 +21011,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:10">
       <c r="A574" t="s">
         <v>64</v>
       </c>
@@ -21093,7 +21043,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:10">
       <c r="A575" t="s">
         <v>64</v>
       </c>
@@ -21125,7 +21075,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:10">
       <c r="A576" t="s">
         <v>65</v>
       </c>
@@ -21157,7 +21107,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:10">
       <c r="A577" t="s">
         <v>65</v>
       </c>
@@ -21189,7 +21139,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:10">
       <c r="A578" t="s">
         <v>65</v>
       </c>
@@ -21221,7 +21171,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:10">
       <c r="A579" t="s">
         <v>65</v>
       </c>
@@ -21253,7 +21203,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:10">
       <c r="A580" t="s">
         <v>65</v>
       </c>
@@ -21285,7 +21235,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:10">
       <c r="A581" t="s">
         <v>65</v>
       </c>
@@ -21317,7 +21267,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:10">
       <c r="A582" t="s">
         <v>65</v>
       </c>
@@ -21349,7 +21299,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:10">
       <c r="A583" t="s">
         <v>65</v>
       </c>
@@ -21381,7 +21331,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:10">
       <c r="A584" t="s">
         <v>66</v>
       </c>
@@ -21413,7 +21363,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:10">
       <c r="A585" t="s">
         <v>66</v>
       </c>
@@ -21445,7 +21395,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:10">
       <c r="A586" t="s">
         <v>66</v>
       </c>
@@ -21477,7 +21427,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:10">
       <c r="A587" t="s">
         <v>66</v>
       </c>
@@ -21509,7 +21459,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:10">
       <c r="A588" t="s">
         <v>66</v>
       </c>
@@ -21541,7 +21491,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:10">
       <c r="A589" t="s">
         <v>67</v>
       </c>
@@ -21573,7 +21523,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:10">
       <c r="A590" t="s">
         <v>67</v>
       </c>
@@ -21605,7 +21555,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:10">
       <c r="A591" t="s">
         <v>67</v>
       </c>
@@ -21637,7 +21587,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:10">
       <c r="A592" t="s">
         <v>67</v>
       </c>
@@ -21669,7 +21619,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:10">
       <c r="A593" t="s">
         <v>67</v>
       </c>
@@ -21701,7 +21651,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:10">
       <c r="A594" t="s">
         <v>67</v>
       </c>
@@ -21733,7 +21683,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:10">
       <c r="A595" t="s">
         <v>67</v>
       </c>
@@ -21765,7 +21715,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:10">
       <c r="A596" t="s">
         <v>68</v>
       </c>
@@ -21797,7 +21747,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:10">
       <c r="A597" t="s">
         <v>68</v>
       </c>
@@ -21829,7 +21779,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:10">
       <c r="A598" t="s">
         <v>68</v>
       </c>
@@ -21861,7 +21811,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:10">
       <c r="A599" t="s">
         <v>68</v>
       </c>
@@ -21893,7 +21843,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:10">
       <c r="A600" t="s">
         <v>68</v>
       </c>
@@ -21925,7 +21875,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:10">
       <c r="A601" t="s">
         <v>68</v>
       </c>
@@ -21957,7 +21907,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:10">
       <c r="A602" t="s">
         <v>68</v>
       </c>
@@ -21989,7 +21939,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:10">
       <c r="A603" t="s">
         <v>68</v>
       </c>
@@ -22021,7 +21971,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:10">
       <c r="A604" t="s">
         <v>68</v>
       </c>
@@ -22053,7 +22003,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:10">
       <c r="A605" t="s">
         <v>69</v>
       </c>
@@ -22085,7 +22035,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:10">
       <c r="A606" t="s">
         <v>69</v>
       </c>
@@ -22117,7 +22067,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:10">
       <c r="A607" t="s">
         <v>69</v>
       </c>
@@ -22149,7 +22099,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:10">
       <c r="A608" t="s">
         <v>69</v>
       </c>
@@ -22181,7 +22131,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="609" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:10">
       <c r="A609" t="s">
         <v>69</v>
       </c>
@@ -22213,7 +22163,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="610" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:10">
       <c r="A610" t="s">
         <v>69</v>
       </c>
@@ -22245,7 +22195,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="611" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:10">
       <c r="A611" t="s">
         <v>69</v>
       </c>
@@ -22277,7 +22227,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="612" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:10">
       <c r="A612" t="s">
         <v>69</v>
       </c>
@@ -22309,7 +22259,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="613" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:10">
       <c r="A613" t="s">
         <v>69</v>
       </c>
@@ -22341,7 +22291,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="614" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:10">
       <c r="A614" t="s">
         <v>69</v>
       </c>
@@ -22373,7 +22323,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="615" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:10">
       <c r="A615" t="s">
         <v>70</v>
       </c>
@@ -22405,7 +22355,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="616" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:10">
       <c r="A616" t="s">
         <v>70</v>
       </c>
@@ -22437,7 +22387,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="617" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:10">
       <c r="A617" t="s">
         <v>70</v>
       </c>
@@ -22469,7 +22419,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="618" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:10">
       <c r="A618" t="s">
         <v>70</v>
       </c>
@@ -22501,7 +22451,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="619" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:10">
       <c r="A619" t="s">
         <v>70</v>
       </c>
@@ -22533,7 +22483,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="620" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:10">
       <c r="A620" t="s">
         <v>70</v>
       </c>
@@ -22565,7 +22515,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="621" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:10">
       <c r="A621" t="s">
         <v>70</v>
       </c>
@@ -22597,7 +22547,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="622" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:10">
       <c r="A622" t="s">
         <v>70</v>
       </c>
@@ -22629,7 +22579,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="623" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:10">
       <c r="A623" t="s">
         <v>70</v>
       </c>
@@ -22661,7 +22611,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="624" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:10">
       <c r="A624" t="s">
         <v>71</v>
       </c>
@@ -22693,7 +22643,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="625" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:10">
       <c r="A625" t="s">
         <v>71</v>
       </c>
@@ -22725,7 +22675,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="626" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:10">
       <c r="A626" t="s">
         <v>71</v>
       </c>
@@ -22757,7 +22707,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="627" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:10">
       <c r="A627" t="s">
         <v>72</v>
       </c>
@@ -22789,7 +22739,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="628" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:10">
       <c r="A628" t="s">
         <v>72</v>
       </c>
@@ -22821,7 +22771,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="629" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:10">
       <c r="A629" t="s">
         <v>72</v>
       </c>
@@ -22853,7 +22803,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="630" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:10">
       <c r="A630" t="s">
         <v>72</v>
       </c>
@@ -22885,7 +22835,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="631" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:10">
       <c r="A631" t="s">
         <v>72</v>
       </c>
@@ -22917,7 +22867,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="632" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:10">
       <c r="A632" t="s">
         <v>73</v>
       </c>
@@ -22949,7 +22899,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="633" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:10">
       <c r="A633" t="s">
         <v>73</v>
       </c>
@@ -22981,7 +22931,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="634" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:10">
       <c r="A634" t="s">
         <v>73</v>
       </c>
@@ -23013,7 +22963,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="635" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:10">
       <c r="A635" t="s">
         <v>73</v>
       </c>
@@ -23045,7 +22995,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="636" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:10">
       <c r="A636" t="s">
         <v>73</v>
       </c>
@@ -23077,7 +23027,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="637" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:10">
       <c r="A637" t="s">
         <v>73</v>
       </c>
@@ -23109,7 +23059,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="638" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:10">
       <c r="A638" t="s">
         <v>73</v>
       </c>
@@ -23141,7 +23091,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="639" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:10">
       <c r="A639" t="s">
         <v>73</v>
       </c>
@@ -23173,7 +23123,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="640" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:10">
       <c r="A640" t="s">
         <v>74</v>
       </c>
@@ -23205,7 +23155,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:10">
       <c r="A641" t="s">
         <v>74</v>
       </c>
@@ -23237,7 +23187,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:10">
       <c r="A642" t="s">
         <v>74</v>
       </c>
@@ -23269,7 +23219,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:10">
       <c r="A643" t="s">
         <v>74</v>
       </c>
@@ -23301,7 +23251,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:10">
       <c r="A644" t="s">
         <v>74</v>
       </c>
@@ -23333,7 +23283,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:10">
       <c r="A645" t="s">
         <v>74</v>
       </c>
@@ -23365,7 +23315,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:10">
       <c r="A646" t="s">
         <v>74</v>
       </c>
@@ -23397,7 +23347,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:10">
       <c r="A647" t="s">
         <v>74</v>
       </c>
@@ -23429,7 +23379,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:10">
       <c r="A648" t="s">
         <v>75</v>
       </c>
@@ -23461,7 +23411,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:10">
       <c r="A649" t="s">
         <v>75</v>
       </c>
@@ -23493,7 +23443,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:10">
       <c r="A650" t="s">
         <v>75</v>
       </c>
@@ -23525,7 +23475,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:10">
       <c r="A651" t="s">
         <v>75</v>
       </c>
@@ -23557,7 +23507,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:10">
       <c r="A652" t="s">
         <v>75</v>
       </c>
@@ -23589,7 +23539,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:10">
       <c r="A653" t="s">
         <v>76</v>
       </c>
@@ -23621,7 +23571,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:10">
       <c r="A654" t="s">
         <v>76</v>
       </c>
@@ -23653,7 +23603,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:10">
       <c r="A655" t="s">
         <v>76</v>
       </c>
@@ -23685,7 +23635,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:10">
       <c r="A656" t="s">
         <v>76</v>
       </c>
@@ -23717,7 +23667,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="657" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:10">
       <c r="A657" t="s">
         <v>77</v>
       </c>
@@ -23749,7 +23699,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="658" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:10">
       <c r="A658" t="s">
         <v>77</v>
       </c>
@@ -23781,7 +23731,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="659" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:10">
       <c r="A659" t="s">
         <v>77</v>
       </c>
@@ -23813,7 +23763,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="660" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:10">
       <c r="A660" t="s">
         <v>77</v>
       </c>
@@ -23845,7 +23795,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="661" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:10">
       <c r="A661" t="s">
         <v>77</v>
       </c>
@@ -23877,7 +23827,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="662" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:10">
       <c r="A662" t="s">
         <v>78</v>
       </c>
@@ -23909,7 +23859,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="663" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:10">
       <c r="A663" t="s">
         <v>78</v>
       </c>
@@ -23941,7 +23891,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="664" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:10">
       <c r="A664" t="s">
         <v>78</v>
       </c>
@@ -23973,7 +23923,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="665" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:10">
       <c r="A665" t="s">
         <v>78</v>
       </c>
@@ -24005,7 +23955,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="666" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:10">
       <c r="A666" t="s">
         <v>79</v>
       </c>
@@ -24037,7 +23987,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:10">
       <c r="A667" t="s">
         <v>79</v>
       </c>
@@ -24069,7 +24019,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="668" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:10">
       <c r="A668" t="s">
         <v>79</v>
       </c>
@@ -24101,7 +24051,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:10">
       <c r="A669" t="s">
         <v>79</v>
       </c>
@@ -24133,7 +24083,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:10">
       <c r="A670" t="s">
         <v>79</v>
       </c>
@@ -24165,7 +24115,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:10">
       <c r="A671" t="s">
         <v>79</v>
       </c>
@@ -24197,7 +24147,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:10">
       <c r="A672" t="s">
         <v>79</v>
       </c>
@@ -24229,7 +24179,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:10">
       <c r="A673" t="s">
         <v>79</v>
       </c>
@@ -24261,7 +24211,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:10">
       <c r="A674" t="s">
         <v>79</v>
       </c>
@@ -24293,7 +24243,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:10">
       <c r="A675" t="s">
         <v>79</v>
       </c>
@@ -24325,7 +24275,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:10">
       <c r="A676" t="s">
         <v>79</v>
       </c>
@@ -24357,7 +24307,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:10">
       <c r="A677" t="s">
         <v>79</v>
       </c>
@@ -24389,7 +24339,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:10">
       <c r="A678" t="s">
         <v>80</v>
       </c>
@@ -24421,7 +24371,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="679" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:10">
       <c r="A679" t="s">
         <v>80</v>
       </c>
@@ -24453,7 +24403,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="680" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:10">
       <c r="A680" t="s">
         <v>80</v>
       </c>
@@ -24485,7 +24435,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="681" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:10">
       <c r="A681" t="s">
         <v>81</v>
       </c>
@@ -24517,7 +24467,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:10">
       <c r="A682" t="s">
         <v>81</v>
       </c>
@@ -24549,7 +24499,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:10">
       <c r="A683" t="s">
         <v>81</v>
       </c>
@@ -24581,7 +24531,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:10">
       <c r="A684" t="s">
         <v>82</v>
       </c>
@@ -24613,7 +24563,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:10">
       <c r="A685" t="s">
         <v>82</v>
       </c>
@@ -24645,7 +24595,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:10">
       <c r="A686" t="s">
         <v>82</v>
       </c>
@@ -24677,7 +24627,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:10">
       <c r="A687" t="s">
         <v>82</v>
       </c>
@@ -24709,7 +24659,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="688" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:10">
       <c r="A688" t="s">
         <v>82</v>
       </c>
@@ -24741,7 +24691,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="689" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:10">
       <c r="A689" t="s">
         <v>82</v>
       </c>
@@ -24773,7 +24723,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="690" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:10">
       <c r="A690" t="s">
         <v>83</v>
       </c>
@@ -24805,7 +24755,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="691" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:10">
       <c r="A691" t="s">
         <v>83</v>
       </c>
@@ -24837,7 +24787,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="692" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:10">
       <c r="A692" t="s">
         <v>83</v>
       </c>
@@ -24869,7 +24819,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="693" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:10">
       <c r="A693" t="s">
         <v>83</v>
       </c>
@@ -24901,7 +24851,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="694" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:10">
       <c r="A694" t="s">
         <v>83</v>
       </c>
@@ -24933,7 +24883,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="695" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:10">
       <c r="A695" t="s">
         <v>84</v>
       </c>
@@ -24965,7 +24915,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="696" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:10">
       <c r="A696" t="s">
         <v>84</v>
       </c>
@@ -24997,7 +24947,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="697" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:10">
       <c r="A697" t="s">
         <v>84</v>
       </c>
@@ -25029,7 +24979,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="698" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:10">
       <c r="A698" t="s">
         <v>85</v>
       </c>
@@ -25061,7 +25011,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="699" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:10">
       <c r="A699" t="s">
         <v>85</v>
       </c>
@@ -25093,7 +25043,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="700" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:10">
       <c r="A700" t="s">
         <v>86</v>
       </c>
@@ -25125,7 +25075,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="701" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:10">
       <c r="A701" t="s">
         <v>86</v>
       </c>
@@ -25157,7 +25107,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="702" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:10">
       <c r="A702" t="s">
         <v>86</v>
       </c>
@@ -25189,7 +25139,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="703" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:10">
       <c r="A703" t="s">
         <v>86</v>
       </c>
@@ -25221,7 +25171,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="704" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:10">
       <c r="A704" t="s">
         <v>86</v>
       </c>
@@ -25253,7 +25203,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="705" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:10">
       <c r="A705" t="s">
         <v>86</v>
       </c>
@@ -25285,7 +25235,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="706" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:10">
       <c r="A706" t="s">
         <v>87</v>
       </c>
@@ -25317,7 +25267,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="707" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:10">
       <c r="A707" t="s">
         <v>87</v>
       </c>
@@ -25349,7 +25299,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="708" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:10">
       <c r="A708" t="s">
         <v>87</v>
       </c>
@@ -25381,7 +25331,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="709" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:10">
       <c r="A709" t="s">
         <v>87</v>
       </c>
@@ -25413,7 +25363,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="710" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:10">
       <c r="A710" t="s">
         <v>87</v>
       </c>
@@ -25445,7 +25395,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="711" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:10">
       <c r="A711" t="s">
         <v>87</v>
       </c>
@@ -25477,7 +25427,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="712" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:10">
       <c r="A712" t="s">
         <v>88</v>
       </c>
@@ -25509,7 +25459,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="713" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:10">
       <c r="A713" t="s">
         <v>88</v>
       </c>
@@ -25541,7 +25491,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="714" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:10">
       <c r="A714" t="s">
         <v>88</v>
       </c>
@@ -25573,7 +25523,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="715" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:10">
       <c r="A715" t="s">
         <v>88</v>
       </c>
@@ -25605,7 +25555,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="716" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:10">
       <c r="A716" t="s">
         <v>89</v>
       </c>
@@ -25637,7 +25587,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="717" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:10">
       <c r="A717" t="s">
         <v>89</v>
       </c>
@@ -25669,7 +25619,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="718" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:10">
       <c r="A718" t="s">
         <v>89</v>
       </c>
@@ -25701,7 +25651,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="719" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:10">
       <c r="A719" t="s">
         <v>89</v>
       </c>
@@ -25733,7 +25683,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="720" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:10">
       <c r="A720" t="s">
         <v>89</v>
       </c>
@@ -25765,7 +25715,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:10">
       <c r="A721" t="s">
         <v>89</v>
       </c>
@@ -25797,7 +25747,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:10">
       <c r="A722" t="s">
         <v>89</v>
       </c>
@@ -25829,7 +25779,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:10">
       <c r="A723" t="s">
         <v>89</v>
       </c>
@@ -25861,7 +25811,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="724" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:10">
       <c r="A724" t="s">
         <v>89</v>
       </c>
@@ -25893,7 +25843,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:10">
       <c r="A725" t="s">
         <v>89</v>
       </c>
@@ -25925,7 +25875,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:10">
       <c r="A726" t="s">
         <v>90</v>
       </c>
@@ -25957,7 +25907,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:10">
       <c r="A727" t="s">
         <v>90</v>
       </c>
@@ -25989,7 +25939,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:10">
       <c r="A728" t="s">
         <v>91</v>
       </c>
@@ -26021,7 +25971,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:10">
       <c r="A729" t="s">
         <v>91</v>
       </c>
@@ -26053,7 +26003,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:10">
       <c r="A730" t="s">
         <v>91</v>
       </c>
@@ -26085,7 +26035,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:10">
       <c r="A731" t="s">
         <v>91</v>
       </c>
@@ -26117,7 +26067,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:10">
       <c r="A732" t="s">
         <v>91</v>
       </c>
@@ -26149,7 +26099,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:10">
       <c r="A733" t="s">
         <v>91</v>
       </c>
@@ -26181,7 +26131,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:10">
       <c r="A734" t="s">
         <v>91</v>
       </c>
@@ -26213,7 +26163,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:10">
       <c r="A735" t="s">
         <v>91</v>
       </c>
@@ -26245,7 +26195,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:10">
       <c r="A736" t="s">
         <v>91</v>
       </c>
@@ -26277,7 +26227,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:10">
       <c r="A737" t="s">
         <v>92</v>
       </c>
@@ -26309,7 +26259,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:10">
       <c r="A738" t="s">
         <v>92</v>
       </c>
@@ -26341,7 +26291,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:10">
       <c r="A739" t="s">
         <v>92</v>
       </c>
@@ -26373,7 +26323,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="740" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:10">
       <c r="A740" t="s">
         <v>92</v>
       </c>
@@ -26405,7 +26355,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="741" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:10">
       <c r="A741" t="s">
         <v>92</v>
       </c>
@@ -26437,7 +26387,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="742" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:10">
       <c r="A742" t="s">
         <v>93</v>
       </c>
@@ -26469,7 +26419,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="743" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:10">
       <c r="A743" t="s">
         <v>93</v>
       </c>
@@ -26501,7 +26451,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="744" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:10">
       <c r="A744" t="s">
         <v>94</v>
       </c>
@@ -26533,7 +26483,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="745" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:10">
       <c r="A745" t="s">
         <v>94</v>
       </c>
@@ -26565,7 +26515,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="746" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:10">
       <c r="A746" t="s">
         <v>94</v>
       </c>
@@ -26597,7 +26547,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="747" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:10">
       <c r="A747" t="s">
         <v>94</v>
       </c>
@@ -26629,7 +26579,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="748" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:10">
       <c r="A748" t="s">
         <v>94</v>
       </c>
@@ -26661,7 +26611,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="749" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:10">
       <c r="A749" t="s">
         <v>95</v>
       </c>
@@ -26693,7 +26643,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="750" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:10">
       <c r="A750" t="s">
         <v>95</v>
       </c>
@@ -26725,7 +26675,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="751" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:10">
       <c r="A751" t="s">
         <v>95</v>
       </c>
@@ -26757,7 +26707,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="752" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:10">
       <c r="A752" t="s">
         <v>95</v>
       </c>
@@ -26789,7 +26739,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:10">
       <c r="A753" t="s">
         <v>95</v>
       </c>
@@ -26821,7 +26771,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:10">
       <c r="A754" t="s">
         <v>95</v>
       </c>
@@ -26853,7 +26803,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:10">
       <c r="A755" t="s">
         <v>95</v>
       </c>
@@ -26885,7 +26835,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:10">
       <c r="A756" t="s">
         <v>96</v>
       </c>
@@ -26917,7 +26867,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:10">
       <c r="A757" t="s">
         <v>96</v>
       </c>
@@ -26949,7 +26899,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:10">
       <c r="A758" t="s">
         <v>96</v>
       </c>
@@ -26981,7 +26931,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:10">
       <c r="A759" t="s">
         <v>96</v>
       </c>
@@ -27013,7 +26963,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:10">
       <c r="A760" t="s">
         <v>96</v>
       </c>
@@ -27045,7 +26995,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:10">
       <c r="A761" t="s">
         <v>96</v>
       </c>
@@ -27077,7 +27027,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:10">
       <c r="A762" t="s">
         <v>96</v>
       </c>
@@ -27109,7 +27059,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:10">
       <c r="A763" t="s">
         <v>96</v>
       </c>
@@ -27141,7 +27091,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:10">
       <c r="A764" t="s">
         <v>97</v>
       </c>
@@ -27173,7 +27123,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:10">
       <c r="A765" t="s">
         <v>97</v>
       </c>
@@ -27205,7 +27155,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:10">
       <c r="A766" t="s">
         <v>97</v>
       </c>
@@ -27237,7 +27187,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:10">
       <c r="A767" t="s">
         <v>97</v>
       </c>
@@ -27269,7 +27219,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:10">
       <c r="A768" t="s">
         <v>97</v>
       </c>
@@ -27301,7 +27251,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="769" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:10">
       <c r="A769" t="s">
         <v>98</v>
       </c>
@@ -27333,7 +27283,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="770" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:10">
       <c r="A770" t="s">
         <v>99</v>
       </c>
@@ -27365,7 +27315,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="771" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:10">
       <c r="A771" t="s">
         <v>100</v>
       </c>
@@ -27397,7 +27347,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="772" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:10">
       <c r="A772" t="s">
         <v>100</v>
       </c>
@@ -27429,7 +27379,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="773" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:10">
       <c r="A773" t="s">
         <v>100</v>
       </c>
@@ -27461,7 +27411,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="774" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:10">
       <c r="A774" t="s">
         <v>100</v>
       </c>
@@ -27493,7 +27443,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="775" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:10">
       <c r="A775" t="s">
         <v>100</v>
       </c>
@@ -27525,7 +27475,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="776" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:10">
       <c r="A776" t="s">
         <v>100</v>
       </c>
@@ -27557,7 +27507,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="777" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:10">
       <c r="A777" t="s">
         <v>100</v>
       </c>
@@ -27589,7 +27539,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="778" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:10">
       <c r="A778" t="s">
         <v>101</v>
       </c>
@@ -27621,7 +27571,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="779" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:10">
       <c r="A779" t="s">
         <v>101</v>
       </c>
@@ -27653,7 +27603,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="780" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:10">
       <c r="A780" t="s">
         <v>101</v>
       </c>
@@ -27685,7 +27635,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="781" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:10">
       <c r="A781" t="s">
         <v>101</v>
       </c>
@@ -27717,7 +27667,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="782" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:10">
       <c r="A782" t="s">
         <v>101</v>
       </c>
@@ -27749,7 +27699,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="783" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:10">
       <c r="A783" t="s">
         <v>101</v>
       </c>
@@ -27781,7 +27731,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="784" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:10">
       <c r="A784" t="s">
         <v>101</v>
       </c>
@@ -27813,7 +27763,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="785" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:10">
       <c r="A785" t="s">
         <v>101</v>
       </c>
@@ -27845,7 +27795,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="786" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:10">
       <c r="A786" t="s">
         <v>101</v>
       </c>
@@ -27877,7 +27827,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="787" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:10">
       <c r="A787" t="s">
         <v>102</v>
       </c>
@@ -27909,7 +27859,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="788" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:10">
       <c r="A788" t="s">
         <v>102</v>
       </c>
@@ -27941,7 +27891,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="789" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:10">
       <c r="A789" t="s">
         <v>102</v>
       </c>
@@ -27973,7 +27923,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="790" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:10">
       <c r="A790" t="s">
         <v>102</v>
       </c>
@@ -28005,7 +27955,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="791" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:10">
       <c r="A791" t="s">
         <v>102</v>
       </c>
@@ -28037,7 +27987,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="792" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:10">
       <c r="A792" t="s">
         <v>103</v>
       </c>
@@ -28069,7 +28019,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="793" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:10">
       <c r="A793" t="s">
         <v>103</v>
       </c>
@@ -28101,7 +28051,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="794" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:10">
       <c r="A794" t="s">
         <v>103</v>
       </c>
@@ -28133,7 +28083,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="795" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:10">
       <c r="A795" t="s">
         <v>103</v>
       </c>
@@ -28165,7 +28115,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="796" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:10">
       <c r="A796" t="s">
         <v>103</v>
       </c>
@@ -28197,7 +28147,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="797" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:10">
       <c r="A797" t="s">
         <v>104</v>
       </c>
@@ -28229,7 +28179,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="798" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:10">
       <c r="A798" t="s">
         <v>104</v>
       </c>
@@ -28261,7 +28211,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="799" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:10">
       <c r="A799" t="s">
         <v>104</v>
       </c>
@@ -28293,7 +28243,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="800" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:10">
       <c r="A800" t="s">
         <v>104</v>
       </c>
@@ -28325,7 +28275,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:10">
       <c r="A801" t="s">
         <v>104</v>
       </c>
@@ -28357,7 +28307,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:10">
       <c r="A802" t="s">
         <v>105</v>
       </c>
@@ -28389,7 +28339,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:10">
       <c r="A803" t="s">
         <v>105</v>
       </c>
@@ -28421,7 +28371,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:10">
       <c r="A804" t="s">
         <v>105</v>
       </c>
@@ -28453,7 +28403,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:10">
       <c r="A805" t="s">
         <v>105</v>
       </c>
@@ -28485,7 +28435,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:10">
       <c r="A806" t="s">
         <v>105</v>
       </c>
@@ -28517,7 +28467,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:10">
       <c r="A807" t="s">
         <v>105</v>
       </c>
@@ -28549,7 +28499,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:10">
       <c r="A808" t="s">
         <v>105</v>
       </c>
@@ -28581,7 +28531,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:10">
       <c r="A809" t="s">
         <v>105</v>
       </c>
@@ -28613,7 +28563,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="810" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:10">
       <c r="A810" t="s">
         <v>105</v>
       </c>
@@ -28645,7 +28595,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="811" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:10">
       <c r="A811" t="s">
         <v>105</v>
       </c>
@@ -28677,7 +28627,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="812" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:10">
       <c r="A812" t="s">
         <v>105</v>
       </c>
@@ -28709,7 +28659,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="813" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:10">
       <c r="A813" t="s">
         <v>106</v>
       </c>
@@ -28741,7 +28691,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="814" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:10">
       <c r="A814" t="s">
         <v>106</v>
       </c>
@@ -28773,7 +28723,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="815" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:10">
       <c r="A815" t="s">
         <v>106</v>
       </c>
@@ -28805,7 +28755,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="816" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:10">
       <c r="A816" t="s">
         <v>106</v>
       </c>
@@ -28837,7 +28787,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="817" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:10">
       <c r="A817" t="s">
         <v>106</v>
       </c>
@@ -28869,7 +28819,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="818" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:10">
       <c r="A818" t="s">
         <v>106</v>
       </c>
@@ -28901,7 +28851,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="819" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:10">
       <c r="A819" t="s">
         <v>106</v>
       </c>
@@ -28933,7 +28883,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="820" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:10">
       <c r="A820" t="s">
         <v>107</v>
       </c>
@@ -28965,7 +28915,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="821" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:10">
       <c r="A821" t="s">
         <v>107</v>
       </c>
@@ -28997,7 +28947,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="822" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:10">
       <c r="A822" t="s">
         <v>107</v>
       </c>
@@ -29029,7 +28979,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="823" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:10">
       <c r="A823" t="s">
         <v>107</v>
       </c>
@@ -29061,7 +29011,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="824" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:10">
       <c r="A824" t="s">
         <v>107</v>
       </c>
@@ -29093,7 +29043,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="825" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:10">
       <c r="A825" t="s">
         <v>108</v>
       </c>
@@ -29125,7 +29075,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="826" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:10">
       <c r="A826" t="s">
         <v>109</v>
       </c>
@@ -29157,7 +29107,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="827" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:10">
       <c r="A827" t="s">
         <v>109</v>
       </c>
@@ -29189,7 +29139,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="828" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:10">
       <c r="A828" t="s">
         <v>109</v>
       </c>
@@ -29221,7 +29171,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="829" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:10">
       <c r="A829" t="s">
         <v>109</v>
       </c>
@@ -29253,7 +29203,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="830" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:10">
       <c r="A830" t="s">
         <v>109</v>
       </c>
@@ -29285,7 +29235,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="831" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:10">
       <c r="A831" t="s">
         <v>110</v>
       </c>
@@ -29317,7 +29267,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="832" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:10">
       <c r="A832" t="s">
         <v>110</v>
       </c>
@@ -29349,7 +29299,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="833" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:10">
       <c r="A833" t="s">
         <v>110</v>
       </c>
@@ -29381,7 +29331,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="834" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:10">
       <c r="A834" t="s">
         <v>110</v>
       </c>
@@ -29413,7 +29363,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="835" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:10">
       <c r="A835" t="s">
         <v>110</v>
       </c>
@@ -29445,7 +29395,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="836" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:10">
       <c r="A836" t="s">
         <v>110</v>
       </c>
@@ -29477,7 +29427,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="837" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:10">
       <c r="A837" t="s">
         <v>111</v>
       </c>
@@ -29509,7 +29459,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="838" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:10">
       <c r="A838" t="s">
         <v>111</v>
       </c>
@@ -29541,7 +29491,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="839" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:10">
       <c r="A839" t="s">
         <v>112</v>
       </c>
@@ -29573,7 +29523,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="840" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:10">
       <c r="A840" t="s">
         <v>112</v>
       </c>
@@ -29605,7 +29555,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="841" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:10">
       <c r="A841" t="s">
         <v>112</v>
       </c>
@@ -29637,7 +29587,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="842" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:10">
       <c r="A842" t="s">
         <v>112</v>
       </c>
@@ -29669,7 +29619,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="843" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:10">
       <c r="A843" t="s">
         <v>112</v>
       </c>
@@ -29701,7 +29651,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="844" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:10">
       <c r="A844" t="s">
         <v>112</v>
       </c>
@@ -29733,7 +29683,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="845" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:10">
       <c r="A845" t="s">
         <v>112</v>
       </c>
@@ -29765,7 +29715,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="846" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:10">
       <c r="A846" t="s">
         <v>112</v>
       </c>
@@ -29797,7 +29747,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="847" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:10">
       <c r="A847" t="s">
         <v>112</v>
       </c>
@@ -29829,7 +29779,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="848" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:10">
       <c r="A848" t="s">
         <v>112</v>
       </c>
@@ -29861,7 +29811,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="849" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:10">
       <c r="A849" t="s">
         <v>112</v>
       </c>
@@ -29893,7 +29843,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="850" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:10">
       <c r="A850" t="s">
         <v>112</v>
       </c>
@@ -29925,7 +29875,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="851" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:10">
       <c r="A851" t="s">
         <v>113</v>
       </c>
@@ -29957,7 +29907,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="852" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:10">
       <c r="A852" t="s">
         <v>113</v>
       </c>
@@ -29989,7 +29939,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="853" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:10">
       <c r="A853" t="s">
         <v>113</v>
       </c>
@@ -30021,7 +29971,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="854" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:10">
       <c r="A854" t="s">
         <v>113</v>
       </c>
@@ -30053,7 +30003,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="855" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:10">
       <c r="A855" t="s">
         <v>113</v>
       </c>
@@ -30085,7 +30035,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="856" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:10">
       <c r="A856" t="s">
         <v>113</v>
       </c>
@@ -30117,7 +30067,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="857" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:10">
       <c r="A857" t="s">
         <v>113</v>
       </c>
@@ -30149,7 +30099,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="858" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:10">
       <c r="A858" t="s">
         <v>113</v>
       </c>
@@ -30181,7 +30131,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="859" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:10">
       <c r="A859" t="s">
         <v>113</v>
       </c>
@@ -30213,7 +30163,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="860" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:10">
       <c r="A860" t="s">
         <v>113</v>
       </c>
@@ -30245,7 +30195,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="861" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:10">
       <c r="A861" t="s">
         <v>113</v>
       </c>
@@ -30277,7 +30227,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="862" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:10">
       <c r="A862" t="s">
         <v>113</v>
       </c>
@@ -30309,7 +30259,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="863" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:10">
       <c r="A863" t="s">
         <v>113</v>
       </c>
@@ -30341,7 +30291,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="864" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:10">
       <c r="A864" t="s">
         <v>113</v>
       </c>
@@ -30373,7 +30323,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="865" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:10">
       <c r="A865" t="s">
         <v>114</v>
       </c>
@@ -30405,7 +30355,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="866" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:10">
       <c r="A866" t="s">
         <v>114</v>
       </c>
@@ -30437,7 +30387,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="867" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:10">
       <c r="A867" t="s">
         <v>114</v>
       </c>
@@ -30469,7 +30419,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="868" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:10">
       <c r="A868" t="s">
         <v>114</v>
       </c>
@@ -30501,7 +30451,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="869" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:10">
       <c r="A869" t="s">
         <v>115</v>
       </c>
@@ -30533,7 +30483,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="870" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:10">
       <c r="A870" t="s">
         <v>116</v>
       </c>
@@ -30565,7 +30515,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="871" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:10">
       <c r="A871" t="s">
         <v>116</v>
       </c>
@@ -30597,7 +30547,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="872" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:10">
       <c r="A872" t="s">
         <v>116</v>
       </c>
@@ -30629,7 +30579,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="873" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:10">
       <c r="A873" t="s">
         <v>116</v>
       </c>
@@ -30661,7 +30611,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="874" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:10">
       <c r="A874" t="s">
         <v>116</v>
       </c>
@@ -30693,7 +30643,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="875" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:10">
       <c r="A875" t="s">
         <v>116</v>
       </c>
@@ -30725,7 +30675,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="876" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:10">
       <c r="A876" t="s">
         <v>116</v>
       </c>
@@ -30757,7 +30707,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="877" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:10">
       <c r="A877" t="s">
         <v>116</v>
       </c>
@@ -30789,7 +30739,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="878" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:10">
       <c r="A878" t="s">
         <v>116</v>
       </c>
@@ -30821,7 +30771,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="879" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:10">
       <c r="A879" t="s">
         <v>116</v>
       </c>
@@ -30853,7 +30803,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="880" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:10">
       <c r="A880" t="s">
         <v>116</v>
       </c>
@@ -30885,7 +30835,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="881" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:10">
       <c r="A881" t="s">
         <v>116</v>
       </c>
@@ -30917,7 +30867,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="882" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:10">
       <c r="A882" t="s">
         <v>117</v>
       </c>
@@ -30949,7 +30899,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="883" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:10">
       <c r="A883" t="s">
         <v>117</v>
       </c>
@@ -30981,7 +30931,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="884" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:10">
       <c r="A884" t="s">
         <v>117</v>
       </c>
@@ -31013,7 +30963,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="885" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:10">
       <c r="A885" t="s">
         <v>117</v>
       </c>
@@ -31045,7 +30995,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="886" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:10">
       <c r="A886" t="s">
         <v>117</v>
       </c>
@@ -31077,7 +31027,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="887" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:10">
       <c r="A887" t="s">
         <v>118</v>
       </c>
@@ -31109,7 +31059,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="888" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:10">
       <c r="A888" t="s">
         <v>118</v>
       </c>
@@ -31141,7 +31091,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="889" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:10">
       <c r="A889" t="s">
         <v>118</v>
       </c>
@@ -31173,7 +31123,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="890" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:10">
       <c r="A890" t="s">
         <v>118</v>
       </c>
@@ -31205,7 +31155,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="891" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:10">
       <c r="A891" t="s">
         <v>118</v>
       </c>
@@ -31237,7 +31187,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="892" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:10">
       <c r="A892" t="s">
         <v>119</v>
       </c>
@@ -31269,7 +31219,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="893" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:10">
       <c r="A893" t="s">
         <v>119</v>
       </c>
@@ -31301,7 +31251,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="894" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:10">
       <c r="A894" t="s">
         <v>119</v>
       </c>
@@ -31333,7 +31283,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="895" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:10">
       <c r="A895" t="s">
         <v>119</v>
       </c>
@@ -31365,7 +31315,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="896" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:10">
       <c r="A896" t="s">
         <v>119</v>
       </c>
@@ -31397,7 +31347,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="897" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:10">
       <c r="A897" t="s">
         <v>119</v>
       </c>
@@ -31429,7 +31379,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="898" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:10">
       <c r="A898" t="s">
         <v>119</v>
       </c>
@@ -31461,7 +31411,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="899" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:10">
       <c r="A899" t="s">
         <v>119</v>
       </c>
@@ -31493,7 +31443,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="900" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:10">
       <c r="A900" t="s">
         <v>119</v>
       </c>
@@ -31525,7 +31475,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="901" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:10">
       <c r="A901" t="s">
         <v>119</v>
       </c>
@@ -31557,7 +31507,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="902" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:10">
       <c r="A902" t="s">
         <v>120</v>
       </c>
@@ -31589,7 +31539,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="903" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:10">
       <c r="A903" t="s">
         <v>120</v>
       </c>
@@ -31621,7 +31571,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="904" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:10">
       <c r="A904" t="s">
         <v>120</v>
       </c>
@@ -31653,7 +31603,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="905" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:10">
       <c r="A905" t="s">
         <v>120</v>
       </c>
@@ -31685,7 +31635,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="906" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:10">
       <c r="A906" t="s">
         <v>120</v>
       </c>
@@ -31717,7 +31667,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="907" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:10">
       <c r="A907" t="s">
         <v>121</v>
       </c>
@@ -31749,7 +31699,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="908" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:10">
       <c r="A908" t="s">
         <v>122</v>
       </c>
@@ -31781,7 +31731,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="909" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:10">
       <c r="A909" t="s">
         <v>123</v>
       </c>
@@ -31813,7 +31763,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="910" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:10">
       <c r="A910" t="s">
         <v>123</v>
       </c>
@@ -31845,7 +31795,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="911" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:10">
       <c r="A911" t="s">
         <v>123</v>
       </c>
@@ -31877,7 +31827,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="912" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:10">
       <c r="A912" t="s">
         <v>123</v>
       </c>
@@ -31909,7 +31859,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="913" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:10">
       <c r="A913" t="s">
         <v>124</v>
       </c>
@@ -31941,7 +31891,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="914" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:10">
       <c r="A914" t="s">
         <v>124</v>
       </c>
@@ -31973,7 +31923,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="915" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:10">
       <c r="A915" t="s">
         <v>124</v>
       </c>
@@ -32005,7 +31955,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="916" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:10">
       <c r="A916" t="s">
         <v>124</v>
       </c>
@@ -32037,7 +31987,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="917" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:10">
       <c r="A917" t="s">
         <v>125</v>
       </c>
@@ -32069,7 +32019,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="918" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:10">
       <c r="A918" t="s">
         <v>125</v>
       </c>
@@ -32101,7 +32051,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="919" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:10">
       <c r="A919" t="s">
         <v>125</v>
       </c>
@@ -32133,7 +32083,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="920" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:10">
       <c r="A920" t="s">
         <v>125</v>
       </c>
@@ -32165,7 +32115,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="921" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:10">
       <c r="A921" t="s">
         <v>125</v>
       </c>
@@ -32197,7 +32147,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="922" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:10">
       <c r="A922" t="s">
         <v>125</v>
       </c>
@@ -32229,7 +32179,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="923" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:10">
       <c r="A923" t="s">
         <v>125</v>
       </c>
@@ -32261,7 +32211,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="924" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:10">
       <c r="A924" t="s">
         <v>125</v>
       </c>
@@ -32293,7 +32243,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="925" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:10">
       <c r="A925" t="s">
         <v>126</v>
       </c>
@@ -32325,7 +32275,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="926" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:10">
       <c r="A926" t="s">
         <v>126</v>
       </c>
@@ -32357,7 +32307,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="927" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:10">
       <c r="A927" t="s">
         <v>126</v>
       </c>
@@ -32389,7 +32339,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="928" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:10">
       <c r="A928" t="s">
         <v>126</v>
       </c>
@@ -32421,7 +32371,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="929" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:10">
       <c r="A929" t="s">
         <v>127</v>
       </c>
@@ -32453,7 +32403,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="930" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:10">
       <c r="A930" t="s">
         <v>128</v>
       </c>
@@ -32485,7 +32435,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="931" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:10">
       <c r="A931" t="s">
         <v>128</v>
       </c>
@@ -32517,7 +32467,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="932" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:10">
       <c r="A932" t="s">
         <v>128</v>
       </c>
@@ -32549,7 +32499,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="933" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:10">
       <c r="A933" t="s">
         <v>129</v>
       </c>
@@ -32581,7 +32531,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="934" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:10">
       <c r="A934" t="s">
         <v>129</v>
       </c>
@@ -32613,7 +32563,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="935" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:10">
       <c r="A935" t="s">
         <v>129</v>
       </c>
@@ -32645,7 +32595,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="936" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:10">
       <c r="A936" t="s">
         <v>129</v>
       </c>
@@ -32677,7 +32627,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="937" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:10">
       <c r="A937" t="s">
         <v>129</v>
       </c>
@@ -32709,7 +32659,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="938" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:10">
       <c r="A938" t="s">
         <v>129</v>
       </c>
@@ -32741,7 +32691,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="939" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:10">
       <c r="A939" t="s">
         <v>129</v>
       </c>
@@ -32773,7 +32723,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="940" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:10">
       <c r="A940" t="s">
         <v>129</v>
       </c>
@@ -32805,7 +32755,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="941" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:10">
       <c r="A941" t="s">
         <v>129</v>
       </c>
@@ -32837,7 +32787,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="942" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:10">
       <c r="A942" t="s">
         <v>129</v>
       </c>
@@ -32869,7 +32819,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="943" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:10">
       <c r="A943" t="s">
         <v>129</v>
       </c>

--- a/pages/Sprint_Points_Men.xlsx
+++ b/pages/Sprint_Points_Men.xlsx
@@ -1132,28 +1132,28 @@
     <t>22 Sep 2022</t>
   </si>
   <si>
-    <t>UCI World Championships</t>
-  </si>
-  <si>
-    <t>Nations' Cup</t>
-  </si>
-  <si>
-    <t>Continental Championships</t>
-  </si>
-  <si>
-    <t>TCL General Ranking</t>
-  </si>
-  <si>
-    <t>TCL Round Ranking</t>
-  </si>
-  <si>
-    <t>National Championships</t>
-  </si>
-  <si>
-    <t>Class 1</t>
-  </si>
-  <si>
-    <t>Class 2</t>
+    <t>WCh</t>
+  </si>
+  <si>
+    <t>NCp</t>
+  </si>
+  <si>
+    <t>CCh</t>
+  </si>
+  <si>
+    <t>ChL</t>
+  </si>
+  <si>
+    <t>ChR</t>
+  </si>
+  <si>
+    <t>NCh</t>
+  </si>
+  <si>
+    <t>CL1</t>
+  </si>
+  <si>
+    <t>CL2</t>
   </si>
   <si>
     <t>Tissot UCI Track World Championships - Men Elite - Sprint - General Classification</t>

--- a/pages/Sprint_Points_Men.xlsx
+++ b/pages/Sprint_Points_Men.xlsx
@@ -361,7 +361,7 @@
     <t>MADDERN Jade</t>
   </si>
   <si>
-    <t>HSIAO Shih Hsin</t>
+    <t>蕭 HSIAO 世鑫 Shih Hsin</t>
   </si>
   <si>
     <t>HINZE Carl</t>

--- a/pages/Sprint_Points_Men.xlsx
+++ b/pages/Sprint_Points_Men.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>03 Jun 2023</t>
+          <t>04 Jun 2023</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>12 May 2023</t>
+          <t>15 May 2023</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -24834,7 +24834,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -30346,7 +30346,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>28 Dec 2022</t>
+          <t>31 Dec 2022</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -30970,7 +30970,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -31438,7 +31438,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -31698,7 +31698,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -31750,7 +31750,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -32218,7 +32218,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -32322,7 +32322,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -33050,7 +33050,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -33518,7 +33518,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -33570,7 +33570,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>08 Mar 2023</t>
+          <t>12 Mar 2023</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -35234,7 +35234,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -35650,7 +35650,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -36794,7 +36794,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -37158,7 +37158,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -37314,7 +37314,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -37366,7 +37366,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -37626,7 +37626,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -37678,7 +37678,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -38094,7 +38094,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -38146,7 +38146,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -38198,7 +38198,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>15 May 2023</t>
+          <t>19 May 2023</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -38250,7 +38250,7 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>27 May 2023</t>
+          <t>28 May 2023</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -38562,7 +38562,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -38978,7 +38978,7 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -39030,7 +39030,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -40018,7 +40018,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -40070,7 +40070,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -40122,7 +40122,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -40954,7 +40954,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -41110,7 +41110,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>15 Dec 2022</t>
+          <t>17 Dec 2022</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -41734,7 +41734,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -41838,7 +41838,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -42306,7 +42306,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>08 Mar 2023</t>
+          <t>12 Mar 2023</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -42878,7 +42878,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -43034,7 +43034,7 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>11 Jun 2023</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -44490,7 +44490,7 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -44646,7 +44646,7 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
@@ -45218,7 +45218,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -45426,7 +45426,7 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -45478,7 +45478,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -45894,7 +45894,7 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>03 Jun 2023</t>
+          <t>04 Jun 2023</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
@@ -46102,7 +46102,7 @@
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -46154,7 +46154,7 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -46414,7 +46414,7 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -46674,7 +46674,7 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>04 Jan 2023</t>
+          <t>08 Jan 2023</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -46778,7 +46778,7 @@
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>09 Jun 2023</t>
+          <t>10 Jun 2023</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>21 Apr 2023</t>
+          <t>23 Apr 2023</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -47610,7 +47610,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -47662,7 +47662,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -47766,7 +47766,7 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>01 Jun 2023</t>
+          <t>06 Jun 2023</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -47922,7 +47922,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -48026,7 +48026,7 @@
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -48078,7 +48078,7 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -48130,7 +48130,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -48494,7 +48494,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>27 Jan 2023</t>
+          <t>29 Jan 2023</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -48546,7 +48546,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>20 Jan 2023</t>
+          <t>21 Jan 2023</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -48650,7 +48650,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>27 Dec 2022</t>
+          <t>29 Dec 2022</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -48702,7 +48702,7 @@
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>05 May 2023</t>
+          <t>06 May 2023</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -49118,7 +49118,7 @@
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>19 May 2023</t>
+          <t>20 May 2023</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>04 May 2023</t>
+          <t>07 May 2023</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -49846,7 +49846,7 @@
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>31 Mar 2023</t>
+          <t>02 Apr 2023</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -49898,7 +49898,7 @@
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>24 Mar 2023</t>
+          <t>26 Mar 2023</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>20 May 2023</t>
+          <t>21 May 2023</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
@@ -50106,7 +50106,7 @@
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
@@ -50366,7 +50366,7 @@
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>28 Apr 2023</t>
+          <t>29 Apr 2023</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
@@ -50574,7 +50574,7 @@
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>15 Mar 2023</t>
+          <t>17 Mar 2023</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
@@ -50626,7 +50626,7 @@
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>24 Feb 2023</t>
+          <t>26 Feb 2023</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
